--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI381"/>
+  <dimension ref="A1:AI382"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39153,6 +39153,109 @@
       <c r="AH381" t="inlineStr"/>
       <c r="AI381" t="inlineStr"/>
     </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B382" t="n">
+        <v>745.08</v>
+      </c>
+      <c r="C382" t="n">
+        <v>831</v>
+      </c>
+      <c r="D382" t="inlineStr"/>
+      <c r="E382" t="n">
+        <v>676</v>
+      </c>
+      <c r="F382" t="n">
+        <v>1230</v>
+      </c>
+      <c r="G382" t="n">
+        <v>635.5</v>
+      </c>
+      <c r="H382" t="n">
+        <v>679</v>
+      </c>
+      <c r="I382" t="n">
+        <v>513.5</v>
+      </c>
+      <c r="J382" t="n">
+        <v>580</v>
+      </c>
+      <c r="K382" t="n">
+        <v>1291</v>
+      </c>
+      <c r="L382" t="n">
+        <v>813</v>
+      </c>
+      <c r="M382" t="n">
+        <v>1376</v>
+      </c>
+      <c r="N382" t="n">
+        <v>816</v>
+      </c>
+      <c r="O382" t="n">
+        <v>660</v>
+      </c>
+      <c r="P382" t="n">
+        <v>1282</v>
+      </c>
+      <c r="Q382" t="n">
+        <v>831</v>
+      </c>
+      <c r="R382" t="n">
+        <v>680</v>
+      </c>
+      <c r="S382" t="n">
+        <v>1220</v>
+      </c>
+      <c r="T382" t="n">
+        <v>809</v>
+      </c>
+      <c r="U382" t="n">
+        <v>634</v>
+      </c>
+      <c r="V382" t="n">
+        <v>1240.25</v>
+      </c>
+      <c r="W382" t="n">
+        <v>816</v>
+      </c>
+      <c r="X382" t="n">
+        <v>660</v>
+      </c>
+      <c r="Y382" t="n">
+        <v>1287</v>
+      </c>
+      <c r="Z382" t="n">
+        <v>701</v>
+      </c>
+      <c r="AA382" t="n">
+        <v>612</v>
+      </c>
+      <c r="AB382" t="n">
+        <v>1366</v>
+      </c>
+      <c r="AC382" t="n">
+        <v>723</v>
+      </c>
+      <c r="AD382" t="n">
+        <v>587</v>
+      </c>
+      <c r="AE382" t="n">
+        <v>1303</v>
+      </c>
+      <c r="AF382" t="n">
+        <v>810</v>
+      </c>
+      <c r="AG382" t="n">
+        <v>820</v>
+      </c>
+      <c r="AH382" t="inlineStr"/>
+      <c r="AI382" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI382"/>
+  <dimension ref="A1:AI383"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39256,6 +39256,109 @@
       <c r="AH382" t="inlineStr"/>
       <c r="AI382" t="inlineStr"/>
     </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B383" t="n">
+        <v>740.62</v>
+      </c>
+      <c r="C383" t="n">
+        <v>828</v>
+      </c>
+      <c r="D383" t="inlineStr"/>
+      <c r="E383" t="n">
+        <v>676</v>
+      </c>
+      <c r="F383" t="n">
+        <v>1220</v>
+      </c>
+      <c r="G383" t="n">
+        <v>624.75</v>
+      </c>
+      <c r="H383" t="n">
+        <v>672</v>
+      </c>
+      <c r="I383" t="n">
+        <v>507.25</v>
+      </c>
+      <c r="J383" t="n">
+        <v>555</v>
+      </c>
+      <c r="K383" t="n">
+        <v>1255</v>
+      </c>
+      <c r="L383" t="n">
+        <v>805</v>
+      </c>
+      <c r="M383" t="n">
+        <v>1380</v>
+      </c>
+      <c r="N383" t="n">
+        <v>814</v>
+      </c>
+      <c r="O383" t="n">
+        <v>660</v>
+      </c>
+      <c r="P383" t="n">
+        <v>1282</v>
+      </c>
+      <c r="Q383" t="n">
+        <v>825</v>
+      </c>
+      <c r="R383" t="n">
+        <v>680</v>
+      </c>
+      <c r="S383" t="n">
+        <v>1205</v>
+      </c>
+      <c r="T383" t="n">
+        <v>823.25</v>
+      </c>
+      <c r="U383" t="n">
+        <v>650</v>
+      </c>
+      <c r="V383" t="n">
+        <v>1249.25</v>
+      </c>
+      <c r="W383" t="n">
+        <v>814</v>
+      </c>
+      <c r="X383" t="n">
+        <v>660</v>
+      </c>
+      <c r="Y383" t="n">
+        <v>1287</v>
+      </c>
+      <c r="Z383" t="n">
+        <v>686</v>
+      </c>
+      <c r="AA383" t="n">
+        <v>600</v>
+      </c>
+      <c r="AB383" t="n">
+        <v>1349</v>
+      </c>
+      <c r="AC383" t="n">
+        <v>720</v>
+      </c>
+      <c r="AD383" t="n">
+        <v>580</v>
+      </c>
+      <c r="AE383" t="n">
+        <v>1268</v>
+      </c>
+      <c r="AF383" t="n">
+        <v>803.26</v>
+      </c>
+      <c r="AG383" t="n">
+        <v>813</v>
+      </c>
+      <c r="AH383" t="inlineStr"/>
+      <c r="AI383" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI383"/>
+  <dimension ref="A1:AI384"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39359,6 +39359,109 @@
       <c r="AH383" t="inlineStr"/>
       <c r="AI383" t="inlineStr"/>
     </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B384" t="n">
+        <v>721.51</v>
+      </c>
+      <c r="C384" t="n">
+        <v>808</v>
+      </c>
+      <c r="D384" t="inlineStr"/>
+      <c r="E384" t="n">
+        <v>656</v>
+      </c>
+      <c r="F384" t="n">
+        <v>1185</v>
+      </c>
+      <c r="G384" t="n">
+        <v>608</v>
+      </c>
+      <c r="H384" t="n">
+        <v>659</v>
+      </c>
+      <c r="I384" t="n">
+        <v>489.5</v>
+      </c>
+      <c r="J384" t="n">
+        <v>550</v>
+      </c>
+      <c r="K384" t="n">
+        <v>1235</v>
+      </c>
+      <c r="L384" t="n">
+        <v>775</v>
+      </c>
+      <c r="M384" t="n">
+        <v>1382</v>
+      </c>
+      <c r="N384" t="n">
+        <v>798</v>
+      </c>
+      <c r="O384" t="n">
+        <v>651</v>
+      </c>
+      <c r="P384" t="n">
+        <v>1232</v>
+      </c>
+      <c r="Q384" t="n">
+        <v>806</v>
+      </c>
+      <c r="R384" t="n">
+        <v>673</v>
+      </c>
+      <c r="S384" t="n">
+        <v>1165</v>
+      </c>
+      <c r="T384" t="n">
+        <v>780</v>
+      </c>
+      <c r="U384" t="n">
+        <v>657</v>
+      </c>
+      <c r="V384" t="n">
+        <v>1220.25</v>
+      </c>
+      <c r="W384" t="n">
+        <v>798</v>
+      </c>
+      <c r="X384" t="n">
+        <v>651</v>
+      </c>
+      <c r="Y384" t="n">
+        <v>1237</v>
+      </c>
+      <c r="Z384" t="n">
+        <v>682</v>
+      </c>
+      <c r="AA384" t="n">
+        <v>582</v>
+      </c>
+      <c r="AB384" t="n">
+        <v>1330</v>
+      </c>
+      <c r="AC384" t="n">
+        <v>705</v>
+      </c>
+      <c r="AD384" t="n">
+        <v>565</v>
+      </c>
+      <c r="AE384" t="n">
+        <v>1262</v>
+      </c>
+      <c r="AF384" t="n">
+        <v>789.84</v>
+      </c>
+      <c r="AG384" t="n">
+        <v>800</v>
+      </c>
+      <c r="AH384" t="inlineStr"/>
+      <c r="AI384" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI384"/>
+  <dimension ref="A1:AI385"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39462,6 +39462,109 @@
       <c r="AH384" t="inlineStr"/>
       <c r="AI384" t="inlineStr"/>
     </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B385" t="n">
+        <v>689.59</v>
+      </c>
+      <c r="C385" t="n">
+        <v>762</v>
+      </c>
+      <c r="D385" t="inlineStr"/>
+      <c r="E385" t="n">
+        <v>625</v>
+      </c>
+      <c r="F385" t="n">
+        <v>1111</v>
+      </c>
+      <c r="G385" t="n">
+        <v>604.25</v>
+      </c>
+      <c r="H385" t="n">
+        <v>640</v>
+      </c>
+      <c r="I385" t="n">
+        <v>493.25</v>
+      </c>
+      <c r="J385" t="n">
+        <v>530</v>
+      </c>
+      <c r="K385" t="n">
+        <v>1190</v>
+      </c>
+      <c r="L385" t="n">
+        <v>761</v>
+      </c>
+      <c r="M385" t="n">
+        <v>1382</v>
+      </c>
+      <c r="N385" t="n">
+        <v>765</v>
+      </c>
+      <c r="O385" t="n">
+        <v>621</v>
+      </c>
+      <c r="P385" t="n">
+        <v>1164</v>
+      </c>
+      <c r="Q385" t="n">
+        <v>774</v>
+      </c>
+      <c r="R385" t="n">
+        <v>651</v>
+      </c>
+      <c r="S385" t="n">
+        <v>1100</v>
+      </c>
+      <c r="T385" t="n">
+        <v>757</v>
+      </c>
+      <c r="U385" t="n">
+        <v>645</v>
+      </c>
+      <c r="V385" t="n">
+        <v>1165.25</v>
+      </c>
+      <c r="W385" t="n">
+        <v>765</v>
+      </c>
+      <c r="X385" t="n">
+        <v>621</v>
+      </c>
+      <c r="Y385" t="n">
+        <v>1169</v>
+      </c>
+      <c r="Z385" t="n">
+        <v>679</v>
+      </c>
+      <c r="AA385" t="n">
+        <v>585</v>
+      </c>
+      <c r="AB385" t="n">
+        <v>1293</v>
+      </c>
+      <c r="AC385" t="n">
+        <v>698</v>
+      </c>
+      <c r="AD385" t="n">
+        <v>561</v>
+      </c>
+      <c r="AE385" t="n">
+        <v>1252</v>
+      </c>
+      <c r="AF385" t="n">
+        <v>764.8200000000001</v>
+      </c>
+      <c r="AG385" t="n">
+        <v>775</v>
+      </c>
+      <c r="AH385" t="inlineStr"/>
+      <c r="AI385" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI385"/>
+  <dimension ref="A1:AI386"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39565,6 +39565,109 @@
       <c r="AH385" t="inlineStr"/>
       <c r="AI385" t="inlineStr"/>
     </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B386" t="n">
+        <v>699.08</v>
+      </c>
+      <c r="C386" t="n">
+        <v>775</v>
+      </c>
+      <c r="D386" t="inlineStr"/>
+      <c r="E386" t="n">
+        <v>620</v>
+      </c>
+      <c r="F386" t="n">
+        <v>1132</v>
+      </c>
+      <c r="G386" t="n">
+        <v>610.75</v>
+      </c>
+      <c r="H386" t="n">
+        <v>643</v>
+      </c>
+      <c r="I386" t="n">
+        <v>487.5</v>
+      </c>
+      <c r="J386" t="n">
+        <v>531</v>
+      </c>
+      <c r="K386" t="n">
+        <v>1208</v>
+      </c>
+      <c r="L386" t="n">
+        <v>770</v>
+      </c>
+      <c r="M386" t="n">
+        <v>1380</v>
+      </c>
+      <c r="N386" t="n">
+        <v>772</v>
+      </c>
+      <c r="O386" t="n">
+        <v>620</v>
+      </c>
+      <c r="P386" t="n">
+        <v>1185</v>
+      </c>
+      <c r="Q386" t="n">
+        <v>782</v>
+      </c>
+      <c r="R386" t="n">
+        <v>648</v>
+      </c>
+      <c r="S386" t="n">
+        <v>1125</v>
+      </c>
+      <c r="T386" t="n">
+        <v>795.75</v>
+      </c>
+      <c r="U386" t="n">
+        <v>678.5</v>
+      </c>
+      <c r="V386" t="n">
+        <v>1231</v>
+      </c>
+      <c r="W386" t="n">
+        <v>772</v>
+      </c>
+      <c r="X386" t="n">
+        <v>620</v>
+      </c>
+      <c r="Y386" t="n">
+        <v>1190</v>
+      </c>
+      <c r="Z386" t="n">
+        <v>690</v>
+      </c>
+      <c r="AA386" t="n">
+        <v>580</v>
+      </c>
+      <c r="AB386" t="n">
+        <v>1315</v>
+      </c>
+      <c r="AC386" t="n">
+        <v>695</v>
+      </c>
+      <c r="AD386" t="n">
+        <v>566</v>
+      </c>
+      <c r="AE386" t="n">
+        <v>1207</v>
+      </c>
+      <c r="AF386" t="n">
+        <v>771.02</v>
+      </c>
+      <c r="AG386" t="n">
+        <v>781</v>
+      </c>
+      <c r="AH386" t="inlineStr"/>
+      <c r="AI386" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI386"/>
+  <dimension ref="A1:AI387"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39668,6 +39668,109 @@
       <c r="AH386" t="inlineStr"/>
       <c r="AI386" t="inlineStr"/>
     </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B387" t="n">
+        <v>715</v>
+      </c>
+      <c r="C387" t="n">
+        <v>791</v>
+      </c>
+      <c r="D387" t="inlineStr"/>
+      <c r="E387" t="n">
+        <v>611</v>
+      </c>
+      <c r="F387" t="n">
+        <v>1150</v>
+      </c>
+      <c r="G387" t="n">
+        <v>614.75</v>
+      </c>
+      <c r="H387" t="n">
+        <v>660</v>
+      </c>
+      <c r="I387" t="n">
+        <v>495.75</v>
+      </c>
+      <c r="J387" t="n">
+        <v>538</v>
+      </c>
+      <c r="K387" t="n">
+        <v>1222</v>
+      </c>
+      <c r="L387" t="n">
+        <v>780</v>
+      </c>
+      <c r="M387" t="n">
+        <v>1381</v>
+      </c>
+      <c r="N387" t="n">
+        <v>785</v>
+      </c>
+      <c r="O387" t="n">
+        <v>614</v>
+      </c>
+      <c r="P387" t="n">
+        <v>1201</v>
+      </c>
+      <c r="Q387" t="n">
+        <v>793</v>
+      </c>
+      <c r="R387" t="n">
+        <v>660</v>
+      </c>
+      <c r="S387" t="n">
+        <v>1146</v>
+      </c>
+      <c r="T387" t="n">
+        <v>797.25</v>
+      </c>
+      <c r="U387" t="n">
+        <v>670</v>
+      </c>
+      <c r="V387" t="n">
+        <v>1220.25</v>
+      </c>
+      <c r="W387" t="n">
+        <v>785</v>
+      </c>
+      <c r="X387" t="n">
+        <v>614</v>
+      </c>
+      <c r="Y387" t="n">
+        <v>1206</v>
+      </c>
+      <c r="Z387" t="n">
+        <v>695</v>
+      </c>
+      <c r="AA387" t="n">
+        <v>577</v>
+      </c>
+      <c r="AB387" t="n">
+        <v>1328</v>
+      </c>
+      <c r="AC387" t="n">
+        <v>692</v>
+      </c>
+      <c r="AD387" t="n">
+        <v>622</v>
+      </c>
+      <c r="AE387" t="n">
+        <v>1212</v>
+      </c>
+      <c r="AF387" t="n">
+        <v>786.71</v>
+      </c>
+      <c r="AG387" t="n">
+        <v>797</v>
+      </c>
+      <c r="AH387" t="inlineStr"/>
+      <c r="AI387" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI387"/>
+  <dimension ref="A1:AI388"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39771,6 +39771,93 @@
       <c r="AH387" t="inlineStr"/>
       <c r="AI387" t="inlineStr"/>
     </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B388" t="n">
+        <v>746.25</v>
+      </c>
+      <c r="C388" t="n">
+        <v>822</v>
+      </c>
+      <c r="D388" t="inlineStr"/>
+      <c r="E388" t="n">
+        <v>623</v>
+      </c>
+      <c r="F388" t="n">
+        <v>1199.25</v>
+      </c>
+      <c r="G388" t="inlineStr"/>
+      <c r="H388" t="inlineStr"/>
+      <c r="I388" t="inlineStr"/>
+      <c r="J388" t="inlineStr"/>
+      <c r="K388" t="inlineStr"/>
+      <c r="L388" t="n">
+        <v>811</v>
+      </c>
+      <c r="M388" t="n">
+        <v>1374</v>
+      </c>
+      <c r="N388" t="n">
+        <v>805</v>
+      </c>
+      <c r="O388" t="n">
+        <v>621</v>
+      </c>
+      <c r="P388" t="n">
+        <v>1234</v>
+      </c>
+      <c r="Q388" t="n">
+        <v>824</v>
+      </c>
+      <c r="R388" t="n">
+        <v>677</v>
+      </c>
+      <c r="S388" t="n">
+        <v>1179</v>
+      </c>
+      <c r="T388" t="n">
+        <v>840</v>
+      </c>
+      <c r="U388" t="n">
+        <v>685</v>
+      </c>
+      <c r="V388" t="n">
+        <v>1230.25</v>
+      </c>
+      <c r="W388" t="n">
+        <v>805</v>
+      </c>
+      <c r="X388" t="n">
+        <v>621</v>
+      </c>
+      <c r="Y388" t="n">
+        <v>1239</v>
+      </c>
+      <c r="Z388" t="inlineStr"/>
+      <c r="AA388" t="inlineStr"/>
+      <c r="AB388" t="inlineStr"/>
+      <c r="AC388" t="n">
+        <v>706</v>
+      </c>
+      <c r="AD388" t="n">
+        <v>628</v>
+      </c>
+      <c r="AE388" t="n">
+        <v>1232</v>
+      </c>
+      <c r="AF388" t="n">
+        <v>819.96</v>
+      </c>
+      <c r="AG388" t="n">
+        <v>830</v>
+      </c>
+      <c r="AH388" t="inlineStr"/>
+      <c r="AI388" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI388"/>
+  <dimension ref="A1:AI389"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39858,6 +39858,103 @@
       <c r="AH388" t="inlineStr"/>
       <c r="AI388" t="inlineStr"/>
     </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B389" t="n">
+        <v>770.04</v>
+      </c>
+      <c r="C389" t="n">
+        <v>844</v>
+      </c>
+      <c r="D389" t="inlineStr"/>
+      <c r="E389" t="n">
+        <v>639</v>
+      </c>
+      <c r="F389" t="n">
+        <v>1218</v>
+      </c>
+      <c r="G389" t="n">
+        <v>625.5</v>
+      </c>
+      <c r="H389" t="n">
+        <v>682</v>
+      </c>
+      <c r="I389" t="inlineStr"/>
+      <c r="J389" t="n">
+        <v>556</v>
+      </c>
+      <c r="K389" t="n">
+        <v>1348</v>
+      </c>
+      <c r="L389" t="n">
+        <v>836</v>
+      </c>
+      <c r="M389" t="n">
+        <v>1377</v>
+      </c>
+      <c r="N389" t="n">
+        <v>820</v>
+      </c>
+      <c r="O389" t="n">
+        <v>635</v>
+      </c>
+      <c r="P389" t="n">
+        <v>1265</v>
+      </c>
+      <c r="Q389" t="n">
+        <v>848</v>
+      </c>
+      <c r="R389" t="n">
+        <v>696</v>
+      </c>
+      <c r="S389" t="n">
+        <v>1217</v>
+      </c>
+      <c r="T389" t="n">
+        <v>905</v>
+      </c>
+      <c r="U389" t="n">
+        <v>694</v>
+      </c>
+      <c r="V389" t="n">
+        <v>1258.25</v>
+      </c>
+      <c r="W389" t="n">
+        <v>820</v>
+      </c>
+      <c r="X389" t="n">
+        <v>635</v>
+      </c>
+      <c r="Y389" t="n">
+        <v>1270</v>
+      </c>
+      <c r="Z389" t="n">
+        <v>706</v>
+      </c>
+      <c r="AA389" t="inlineStr"/>
+      <c r="AB389" t="inlineStr"/>
+      <c r="AC389" t="n">
+        <v>722</v>
+      </c>
+      <c r="AD389" t="n">
+        <v>589</v>
+      </c>
+      <c r="AE389" t="n">
+        <v>1382</v>
+      </c>
+      <c r="AF389" t="n">
+        <v>834.75</v>
+      </c>
+      <c r="AG389" t="n">
+        <v>845</v>
+      </c>
+      <c r="AH389" t="inlineStr"/>
+      <c r="AI389" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI389"/>
+  <dimension ref="A1:AI390"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39955,6 +39955,103 @@
       <c r="AH389" t="inlineStr"/>
       <c r="AI389" t="inlineStr"/>
     </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B390" t="n">
+        <v>785.67</v>
+      </c>
+      <c r="C390" t="n">
+        <v>855</v>
+      </c>
+      <c r="D390" t="inlineStr"/>
+      <c r="E390" t="n">
+        <v>636</v>
+      </c>
+      <c r="F390" t="n">
+        <v>1240</v>
+      </c>
+      <c r="G390" t="n">
+        <v>627.75</v>
+      </c>
+      <c r="H390" t="n">
+        <v>680</v>
+      </c>
+      <c r="I390" t="inlineStr"/>
+      <c r="J390" t="n">
+        <v>568</v>
+      </c>
+      <c r="K390" t="n">
+        <v>1375</v>
+      </c>
+      <c r="L390" t="n">
+        <v>853</v>
+      </c>
+      <c r="M390" t="n">
+        <v>1381</v>
+      </c>
+      <c r="N390" t="n">
+        <v>835</v>
+      </c>
+      <c r="O390" t="n">
+        <v>650</v>
+      </c>
+      <c r="P390" t="n">
+        <v>1290</v>
+      </c>
+      <c r="Q390" t="n">
+        <v>864</v>
+      </c>
+      <c r="R390" t="n">
+        <v>693</v>
+      </c>
+      <c r="S390" t="n">
+        <v>1247</v>
+      </c>
+      <c r="T390" t="n">
+        <v>960</v>
+      </c>
+      <c r="U390" t="n">
+        <v>693</v>
+      </c>
+      <c r="V390" t="n">
+        <v>1318.75</v>
+      </c>
+      <c r="W390" t="n">
+        <v>835</v>
+      </c>
+      <c r="X390" t="n">
+        <v>650</v>
+      </c>
+      <c r="Y390" t="n">
+        <v>1295</v>
+      </c>
+      <c r="Z390" t="n">
+        <v>699</v>
+      </c>
+      <c r="AA390" t="inlineStr"/>
+      <c r="AB390" t="inlineStr"/>
+      <c r="AC390" t="n">
+        <v>728</v>
+      </c>
+      <c r="AD390" t="n">
+        <v>618</v>
+      </c>
+      <c r="AE390" t="n">
+        <v>1386</v>
+      </c>
+      <c r="AF390" t="n">
+        <v>850.08</v>
+      </c>
+      <c r="AG390" t="n">
+        <v>860</v>
+      </c>
+      <c r="AH390" t="inlineStr"/>
+      <c r="AI390" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI390"/>
+  <dimension ref="A1:AI391"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40052,6 +40052,103 @@
       <c r="AH390" t="inlineStr"/>
       <c r="AI390" t="inlineStr"/>
     </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B391" t="n">
+        <v>778.65</v>
+      </c>
+      <c r="C391" t="n">
+        <v>843</v>
+      </c>
+      <c r="D391" t="inlineStr"/>
+      <c r="E391" t="n">
+        <v>632</v>
+      </c>
+      <c r="F391" t="n">
+        <v>1262</v>
+      </c>
+      <c r="G391" t="n">
+        <v>618.25</v>
+      </c>
+      <c r="H391" t="n">
+        <v>674</v>
+      </c>
+      <c r="I391" t="inlineStr"/>
+      <c r="J391" t="n">
+        <v>574</v>
+      </c>
+      <c r="K391" t="n">
+        <v>1368</v>
+      </c>
+      <c r="L391" t="n">
+        <v>846</v>
+      </c>
+      <c r="M391" t="n">
+        <v>1385</v>
+      </c>
+      <c r="N391" t="n">
+        <v>825</v>
+      </c>
+      <c r="O391" t="n">
+        <v>640</v>
+      </c>
+      <c r="P391" t="n">
+        <v>1280</v>
+      </c>
+      <c r="Q391" t="n">
+        <v>861</v>
+      </c>
+      <c r="R391" t="n">
+        <v>683</v>
+      </c>
+      <c r="S391" t="n">
+        <v>1243</v>
+      </c>
+      <c r="T391" t="n">
+        <v>986.25</v>
+      </c>
+      <c r="U391" t="n">
+        <v>693</v>
+      </c>
+      <c r="V391" t="n">
+        <v>1317.25</v>
+      </c>
+      <c r="W391" t="n">
+        <v>825</v>
+      </c>
+      <c r="X391" t="n">
+        <v>640</v>
+      </c>
+      <c r="Y391" t="n">
+        <v>1285</v>
+      </c>
+      <c r="Z391" t="n">
+        <v>700</v>
+      </c>
+      <c r="AA391" t="inlineStr"/>
+      <c r="AB391" t="inlineStr"/>
+      <c r="AC391" t="n">
+        <v>737</v>
+      </c>
+      <c r="AD391" t="n">
+        <v>632</v>
+      </c>
+      <c r="AE391" t="n">
+        <v>1392</v>
+      </c>
+      <c r="AF391" t="n">
+        <v>839.86</v>
+      </c>
+      <c r="AG391" t="n">
+        <v>850</v>
+      </c>
+      <c r="AH391" t="inlineStr"/>
+      <c r="AI391" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI391"/>
+  <dimension ref="A1:AI392"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40149,6 +40149,103 @@
       <c r="AH391" t="inlineStr"/>
       <c r="AI391" t="inlineStr"/>
     </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B392" t="n">
+        <v>767.74</v>
+      </c>
+      <c r="C392" t="n">
+        <v>833</v>
+      </c>
+      <c r="D392" t="inlineStr"/>
+      <c r="E392" t="n">
+        <v>633</v>
+      </c>
+      <c r="F392" t="n">
+        <v>1232.5</v>
+      </c>
+      <c r="G392" t="n">
+        <v>614.5</v>
+      </c>
+      <c r="H392" t="n">
+        <v>684</v>
+      </c>
+      <c r="I392" t="inlineStr"/>
+      <c r="J392" t="n">
+        <v>584</v>
+      </c>
+      <c r="K392" t="n">
+        <v>1359</v>
+      </c>
+      <c r="L392" t="n">
+        <v>832</v>
+      </c>
+      <c r="M392" t="n">
+        <v>1390</v>
+      </c>
+      <c r="N392" t="n">
+        <v>818</v>
+      </c>
+      <c r="O392" t="n">
+        <v>640</v>
+      </c>
+      <c r="P392" t="n">
+        <v>1268</v>
+      </c>
+      <c r="Q392" t="n">
+        <v>850</v>
+      </c>
+      <c r="R392" t="n">
+        <v>694</v>
+      </c>
+      <c r="S392" t="n">
+        <v>1240</v>
+      </c>
+      <c r="T392" t="n">
+        <v>990.5</v>
+      </c>
+      <c r="U392" t="n">
+        <v>699</v>
+      </c>
+      <c r="V392" t="n">
+        <v>1326.75</v>
+      </c>
+      <c r="W392" t="n">
+        <v>818</v>
+      </c>
+      <c r="X392" t="n">
+        <v>642</v>
+      </c>
+      <c r="Y392" t="n">
+        <v>1273</v>
+      </c>
+      <c r="Z392" t="n">
+        <v>693</v>
+      </c>
+      <c r="AA392" t="inlineStr"/>
+      <c r="AB392" t="inlineStr"/>
+      <c r="AC392" t="n">
+        <v>744</v>
+      </c>
+      <c r="AD392" t="n">
+        <v>633</v>
+      </c>
+      <c r="AE392" t="n">
+        <v>1367</v>
+      </c>
+      <c r="AF392" t="n">
+        <v>828.77</v>
+      </c>
+      <c r="AG392" t="n">
+        <v>839</v>
+      </c>
+      <c r="AH392" t="inlineStr"/>
+      <c r="AI392" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI392"/>
+  <dimension ref="A1:AI393"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40246,6 +40246,93 @@
       <c r="AH392" t="inlineStr"/>
       <c r="AI392" t="inlineStr"/>
     </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B393" t="n">
+        <v>764.08</v>
+      </c>
+      <c r="C393" t="n">
+        <v>832</v>
+      </c>
+      <c r="D393" t="inlineStr"/>
+      <c r="E393" t="n">
+        <v>629</v>
+      </c>
+      <c r="F393" t="n">
+        <v>1240</v>
+      </c>
+      <c r="G393" t="n">
+        <v>634.75</v>
+      </c>
+      <c r="H393" t="n">
+        <v>677</v>
+      </c>
+      <c r="I393" t="inlineStr"/>
+      <c r="J393" t="n">
+        <v>578</v>
+      </c>
+      <c r="K393" t="n">
+        <v>1390</v>
+      </c>
+      <c r="L393" t="inlineStr"/>
+      <c r="M393" t="inlineStr"/>
+      <c r="N393" t="n">
+        <v>825</v>
+      </c>
+      <c r="O393" t="n">
+        <v>637</v>
+      </c>
+      <c r="P393" t="n">
+        <v>1285</v>
+      </c>
+      <c r="Q393" t="n">
+        <v>855</v>
+      </c>
+      <c r="R393" t="n">
+        <v>689</v>
+      </c>
+      <c r="S393" t="n">
+        <v>1253</v>
+      </c>
+      <c r="T393" t="n">
+        <v>977.25</v>
+      </c>
+      <c r="U393" t="n">
+        <v>706</v>
+      </c>
+      <c r="V393" t="n">
+        <v>1317</v>
+      </c>
+      <c r="W393" t="n">
+        <v>825</v>
+      </c>
+      <c r="X393" t="n">
+        <v>638</v>
+      </c>
+      <c r="Y393" t="n">
+        <v>1290</v>
+      </c>
+      <c r="Z393" t="n">
+        <v>705</v>
+      </c>
+      <c r="AA393" t="inlineStr"/>
+      <c r="AB393" t="inlineStr"/>
+      <c r="AC393" t="inlineStr"/>
+      <c r="AD393" t="inlineStr"/>
+      <c r="AE393" t="inlineStr"/>
+      <c r="AF393" t="n">
+        <v>829.92</v>
+      </c>
+      <c r="AG393" t="n">
+        <v>840</v>
+      </c>
+      <c r="AH393" t="inlineStr"/>
+      <c r="AI393" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI393"/>
+  <dimension ref="A1:AI394"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40333,6 +40333,103 @@
       <c r="AH393" t="inlineStr"/>
       <c r="AI393" t="inlineStr"/>
     </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B394" t="n">
+        <v>785.4400000000001</v>
+      </c>
+      <c r="C394" t="n">
+        <v>852</v>
+      </c>
+      <c r="D394" t="inlineStr"/>
+      <c r="E394" t="n">
+        <v>651</v>
+      </c>
+      <c r="F394" t="n">
+        <v>1283</v>
+      </c>
+      <c r="G394" t="n">
+        <v>635</v>
+      </c>
+      <c r="H394" t="n">
+        <v>695</v>
+      </c>
+      <c r="I394" t="inlineStr"/>
+      <c r="J394" t="n">
+        <v>590</v>
+      </c>
+      <c r="K394" t="n">
+        <v>1385</v>
+      </c>
+      <c r="L394" t="n">
+        <v>829</v>
+      </c>
+      <c r="M394" t="n">
+        <v>1385</v>
+      </c>
+      <c r="N394" t="n">
+        <v>840</v>
+      </c>
+      <c r="O394" t="n">
+        <v>657</v>
+      </c>
+      <c r="P394" t="n">
+        <v>1319</v>
+      </c>
+      <c r="Q394" t="n">
+        <v>875</v>
+      </c>
+      <c r="R394" t="n">
+        <v>704</v>
+      </c>
+      <c r="S394" t="n">
+        <v>1283</v>
+      </c>
+      <c r="T394" t="n">
+        <v>950</v>
+      </c>
+      <c r="U394" t="n">
+        <v>722</v>
+      </c>
+      <c r="V394" t="n">
+        <v>1337.25</v>
+      </c>
+      <c r="W394" t="n">
+        <v>840</v>
+      </c>
+      <c r="X394" t="n">
+        <v>658</v>
+      </c>
+      <c r="Y394" t="n">
+        <v>1324</v>
+      </c>
+      <c r="Z394" t="n">
+        <v>718</v>
+      </c>
+      <c r="AA394" t="inlineStr"/>
+      <c r="AB394" t="inlineStr"/>
+      <c r="AC394" t="n">
+        <v>749</v>
+      </c>
+      <c r="AD394" t="n">
+        <v>640</v>
+      </c>
+      <c r="AE394" t="n">
+        <v>1377</v>
+      </c>
+      <c r="AF394" t="n">
+        <v>859.9299999999999</v>
+      </c>
+      <c r="AG394" t="n">
+        <v>870</v>
+      </c>
+      <c r="AH394" t="inlineStr"/>
+      <c r="AI394" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI394"/>
+  <dimension ref="A1:AI395"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40430,6 +40430,103 @@
       <c r="AH394" t="inlineStr"/>
       <c r="AI394" t="inlineStr"/>
     </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B395" t="n">
+        <v>781.85</v>
+      </c>
+      <c r="C395" t="n">
+        <v>844</v>
+      </c>
+      <c r="D395" t="inlineStr"/>
+      <c r="E395" t="n">
+        <v>665</v>
+      </c>
+      <c r="F395" t="n">
+        <v>1260</v>
+      </c>
+      <c r="G395" t="n">
+        <v>638.75</v>
+      </c>
+      <c r="H395" t="n">
+        <v>698</v>
+      </c>
+      <c r="I395" t="inlineStr"/>
+      <c r="J395" t="n">
+        <v>594</v>
+      </c>
+      <c r="K395" t="n">
+        <v>1400</v>
+      </c>
+      <c r="L395" t="n">
+        <v>844</v>
+      </c>
+      <c r="M395" t="n">
+        <v>1391</v>
+      </c>
+      <c r="N395" t="n">
+        <v>840</v>
+      </c>
+      <c r="O395" t="n">
+        <v>671</v>
+      </c>
+      <c r="P395" t="n">
+        <v>1318</v>
+      </c>
+      <c r="Q395" t="n">
+        <v>874</v>
+      </c>
+      <c r="R395" t="n">
+        <v>722</v>
+      </c>
+      <c r="S395" t="n">
+        <v>1275</v>
+      </c>
+      <c r="T395" t="n">
+        <v>961</v>
+      </c>
+      <c r="U395" t="n">
+        <v>751.25</v>
+      </c>
+      <c r="V395" t="n">
+        <v>1361</v>
+      </c>
+      <c r="W395" t="n">
+        <v>840</v>
+      </c>
+      <c r="X395" t="n">
+        <v>671</v>
+      </c>
+      <c r="Y395" t="n">
+        <v>1323</v>
+      </c>
+      <c r="Z395" t="n">
+        <v>725</v>
+      </c>
+      <c r="AA395" t="inlineStr"/>
+      <c r="AB395" t="inlineStr"/>
+      <c r="AC395" t="n">
+        <v>766</v>
+      </c>
+      <c r="AD395" t="n">
+        <v>643</v>
+      </c>
+      <c r="AE395" t="n">
+        <v>1439</v>
+      </c>
+      <c r="AF395" t="n">
+        <v>880.12</v>
+      </c>
+      <c r="AG395" t="n">
+        <v>890</v>
+      </c>
+      <c r="AH395" t="inlineStr"/>
+      <c r="AI395" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI395"/>
+  <dimension ref="A1:AI396"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40527,6 +40527,103 @@
       <c r="AH395" t="inlineStr"/>
       <c r="AI395" t="inlineStr"/>
     </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B396" t="n">
+        <v>789.41</v>
+      </c>
+      <c r="C396" t="n">
+        <v>855</v>
+      </c>
+      <c r="D396" t="inlineStr"/>
+      <c r="E396" t="n">
+        <v>680</v>
+      </c>
+      <c r="F396" t="n">
+        <v>1274</v>
+      </c>
+      <c r="G396" t="n">
+        <v>662</v>
+      </c>
+      <c r="H396" t="n">
+        <v>712</v>
+      </c>
+      <c r="I396" t="inlineStr"/>
+      <c r="J396" t="n">
+        <v>603</v>
+      </c>
+      <c r="K396" t="n">
+        <v>1443</v>
+      </c>
+      <c r="L396" t="n">
+        <v>867</v>
+      </c>
+      <c r="M396" t="n">
+        <v>1389</v>
+      </c>
+      <c r="N396" t="n">
+        <v>842</v>
+      </c>
+      <c r="O396" t="n">
+        <v>693</v>
+      </c>
+      <c r="P396" t="n">
+        <v>1315</v>
+      </c>
+      <c r="Q396" t="n">
+        <v>882</v>
+      </c>
+      <c r="R396" t="n">
+        <v>737</v>
+      </c>
+      <c r="S396" t="n">
+        <v>1280</v>
+      </c>
+      <c r="T396" t="n">
+        <v>967.5</v>
+      </c>
+      <c r="U396" t="n">
+        <v>730</v>
+      </c>
+      <c r="V396" t="n">
+        <v>1348.75</v>
+      </c>
+      <c r="W396" t="n">
+        <v>842</v>
+      </c>
+      <c r="X396" t="n">
+        <v>693</v>
+      </c>
+      <c r="Y396" t="n">
+        <v>1320</v>
+      </c>
+      <c r="Z396" t="n">
+        <v>741</v>
+      </c>
+      <c r="AA396" t="inlineStr"/>
+      <c r="AB396" t="inlineStr"/>
+      <c r="AC396" t="n">
+        <v>834</v>
+      </c>
+      <c r="AD396" t="n">
+        <v>679</v>
+      </c>
+      <c r="AE396" t="n">
+        <v>1529</v>
+      </c>
+      <c r="AF396" t="n">
+        <v>920.0700000000001</v>
+      </c>
+      <c r="AG396" t="n">
+        <v>930</v>
+      </c>
+      <c r="AH396" t="inlineStr"/>
+      <c r="AI396" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI396"/>
+  <dimension ref="A1:AI397"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40624,6 +40624,103 @@
       <c r="AH396" t="inlineStr"/>
       <c r="AI396" t="inlineStr"/>
     </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B397" t="n">
+        <v>820.74</v>
+      </c>
+      <c r="C397" t="n">
+        <v>890</v>
+      </c>
+      <c r="D397" t="inlineStr"/>
+      <c r="E397" t="n">
+        <v>736</v>
+      </c>
+      <c r="F397" t="n">
+        <v>1411.25</v>
+      </c>
+      <c r="G397" t="n">
+        <v>655</v>
+      </c>
+      <c r="H397" t="n">
+        <v>710</v>
+      </c>
+      <c r="I397" t="inlineStr"/>
+      <c r="J397" t="n">
+        <v>612</v>
+      </c>
+      <c r="K397" t="n">
+        <v>1473</v>
+      </c>
+      <c r="L397" t="n">
+        <v>866</v>
+      </c>
+      <c r="M397" t="n">
+        <v>1387</v>
+      </c>
+      <c r="N397" t="n">
+        <v>870</v>
+      </c>
+      <c r="O397" t="n">
+        <v>719</v>
+      </c>
+      <c r="P397" t="n">
+        <v>1435</v>
+      </c>
+      <c r="Q397" t="n">
+        <v>902</v>
+      </c>
+      <c r="R397" t="n">
+        <v>779</v>
+      </c>
+      <c r="S397" t="n">
+        <v>1382</v>
+      </c>
+      <c r="T397" t="n">
+        <v>986.75</v>
+      </c>
+      <c r="U397" t="n">
+        <v>783.75</v>
+      </c>
+      <c r="V397" t="n">
+        <v>1487.25</v>
+      </c>
+      <c r="W397" t="n">
+        <v>870</v>
+      </c>
+      <c r="X397" t="n">
+        <v>719</v>
+      </c>
+      <c r="Y397" t="n">
+        <v>1440</v>
+      </c>
+      <c r="Z397" t="n">
+        <v>738</v>
+      </c>
+      <c r="AA397" t="inlineStr"/>
+      <c r="AB397" t="inlineStr"/>
+      <c r="AC397" t="n">
+        <v>824</v>
+      </c>
+      <c r="AD397" t="n">
+        <v>644</v>
+      </c>
+      <c r="AE397" t="n">
+        <v>1534</v>
+      </c>
+      <c r="AF397" t="n">
+        <v>955.11</v>
+      </c>
+      <c r="AG397" t="n">
+        <v>965</v>
+      </c>
+      <c r="AH397" t="inlineStr"/>
+      <c r="AI397" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI397"/>
+  <dimension ref="A1:AI398"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40721,6 +40721,103 @@
       <c r="AH397" t="inlineStr"/>
       <c r="AI397" t="inlineStr"/>
     </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B398" t="n">
+        <v>831.8099999999999</v>
+      </c>
+      <c r="C398" t="n">
+        <v>890</v>
+      </c>
+      <c r="D398" t="inlineStr"/>
+      <c r="E398" t="n">
+        <v>765</v>
+      </c>
+      <c r="F398" t="n">
+        <v>1430</v>
+      </c>
+      <c r="G398" t="n">
+        <v>667.5</v>
+      </c>
+      <c r="H398" t="n">
+        <v>732</v>
+      </c>
+      <c r="I398" t="inlineStr"/>
+      <c r="J398" t="n">
+        <v>630</v>
+      </c>
+      <c r="K398" t="n">
+        <v>1485</v>
+      </c>
+      <c r="L398" t="n">
+        <v>885</v>
+      </c>
+      <c r="M398" t="n">
+        <v>1390</v>
+      </c>
+      <c r="N398" t="n">
+        <v>893</v>
+      </c>
+      <c r="O398" t="n">
+        <v>750</v>
+      </c>
+      <c r="P398" t="n">
+        <v>1485</v>
+      </c>
+      <c r="Q398" t="n">
+        <v>905</v>
+      </c>
+      <c r="R398" t="n">
+        <v>805</v>
+      </c>
+      <c r="S398" t="n">
+        <v>1405</v>
+      </c>
+      <c r="T398" t="n">
+        <v>960</v>
+      </c>
+      <c r="U398" t="n">
+        <v>810</v>
+      </c>
+      <c r="V398" t="n">
+        <v>1420</v>
+      </c>
+      <c r="W398" t="n">
+        <v>893</v>
+      </c>
+      <c r="X398" t="n">
+        <v>750</v>
+      </c>
+      <c r="Y398" t="n">
+        <v>1490</v>
+      </c>
+      <c r="Z398" t="n">
+        <v>775</v>
+      </c>
+      <c r="AA398" t="inlineStr"/>
+      <c r="AB398" t="inlineStr"/>
+      <c r="AC398" t="n">
+        <v>844</v>
+      </c>
+      <c r="AD398" t="n">
+        <v>639</v>
+      </c>
+      <c r="AE398" t="n">
+        <v>1544</v>
+      </c>
+      <c r="AF398" t="n">
+        <v>974.89</v>
+      </c>
+      <c r="AG398" t="n">
+        <v>985</v>
+      </c>
+      <c r="AH398" t="inlineStr"/>
+      <c r="AI398" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI398"/>
+  <dimension ref="A1:AI399"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40818,6 +40818,103 @@
       <c r="AH398" t="inlineStr"/>
       <c r="AI398" t="inlineStr"/>
     </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B399" t="n">
+        <v>849.51</v>
+      </c>
+      <c r="C399" t="n">
+        <v>907</v>
+      </c>
+      <c r="D399" t="inlineStr"/>
+      <c r="E399" t="n">
+        <v>767</v>
+      </c>
+      <c r="F399" t="n">
+        <v>1436.5</v>
+      </c>
+      <c r="G399" t="n">
+        <v>672</v>
+      </c>
+      <c r="H399" t="n">
+        <v>725</v>
+      </c>
+      <c r="I399" t="inlineStr"/>
+      <c r="J399" t="n">
+        <v>621</v>
+      </c>
+      <c r="K399" t="n">
+        <v>1534</v>
+      </c>
+      <c r="L399" t="n">
+        <v>895</v>
+      </c>
+      <c r="M399" t="n">
+        <v>1379</v>
+      </c>
+      <c r="N399" t="n">
+        <v>900</v>
+      </c>
+      <c r="O399" t="n">
+        <v>780</v>
+      </c>
+      <c r="P399" t="n">
+        <v>1477</v>
+      </c>
+      <c r="Q399" t="n">
+        <v>915</v>
+      </c>
+      <c r="R399" t="n">
+        <v>798</v>
+      </c>
+      <c r="S399" t="n">
+        <v>1397</v>
+      </c>
+      <c r="T399" t="n">
+        <v>998.5</v>
+      </c>
+      <c r="U399" t="n">
+        <v>805</v>
+      </c>
+      <c r="V399" t="n">
+        <v>1450.75</v>
+      </c>
+      <c r="W399" t="n">
+        <v>905</v>
+      </c>
+      <c r="X399" t="n">
+        <v>780</v>
+      </c>
+      <c r="Y399" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Z399" t="n">
+        <v>758</v>
+      </c>
+      <c r="AA399" t="inlineStr"/>
+      <c r="AB399" t="inlineStr"/>
+      <c r="AC399" t="n">
+        <v>854</v>
+      </c>
+      <c r="AD399" t="n">
+        <v>654</v>
+      </c>
+      <c r="AE399" t="n">
+        <v>1584</v>
+      </c>
+      <c r="AF399" t="n">
+        <v>999.89</v>
+      </c>
+      <c r="AG399" t="n">
+        <v>1010</v>
+      </c>
+      <c r="AH399" t="inlineStr"/>
+      <c r="AI399" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI399"/>
+  <dimension ref="A1:AI400"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40915,6 +40915,103 @@
       <c r="AH399" t="inlineStr"/>
       <c r="AI399" t="inlineStr"/>
     </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B400" t="n">
+        <v>860.48</v>
+      </c>
+      <c r="C400" t="n">
+        <v>916</v>
+      </c>
+      <c r="D400" t="inlineStr"/>
+      <c r="E400" t="n">
+        <v>755</v>
+      </c>
+      <c r="F400" t="n">
+        <v>1473.5</v>
+      </c>
+      <c r="G400" t="n">
+        <v>654.5</v>
+      </c>
+      <c r="H400" t="n">
+        <v>713</v>
+      </c>
+      <c r="I400" t="inlineStr"/>
+      <c r="J400" t="n">
+        <v>609</v>
+      </c>
+      <c r="K400" t="n">
+        <v>1529</v>
+      </c>
+      <c r="L400" t="n">
+        <v>900</v>
+      </c>
+      <c r="M400" t="n">
+        <v>1382</v>
+      </c>
+      <c r="N400" t="n">
+        <v>915</v>
+      </c>
+      <c r="O400" t="n">
+        <v>785</v>
+      </c>
+      <c r="P400" t="n">
+        <v>1535</v>
+      </c>
+      <c r="Q400" t="n">
+        <v>925</v>
+      </c>
+      <c r="R400" t="n">
+        <v>795</v>
+      </c>
+      <c r="S400" t="n">
+        <v>1455</v>
+      </c>
+      <c r="T400" t="n">
+        <v>970</v>
+      </c>
+      <c r="U400" t="n">
+        <v>800</v>
+      </c>
+      <c r="V400" t="n">
+        <v>1455</v>
+      </c>
+      <c r="W400" t="n">
+        <v>920</v>
+      </c>
+      <c r="X400" t="n">
+        <v>785</v>
+      </c>
+      <c r="Y400" t="n">
+        <v>1540</v>
+      </c>
+      <c r="Z400" t="n">
+        <v>750</v>
+      </c>
+      <c r="AA400" t="inlineStr"/>
+      <c r="AB400" t="inlineStr"/>
+      <c r="AC400" t="n">
+        <v>844</v>
+      </c>
+      <c r="AD400" t="n">
+        <v>644</v>
+      </c>
+      <c r="AE400" t="n">
+        <v>1544</v>
+      </c>
+      <c r="AF400" t="n">
+        <v>1019.61</v>
+      </c>
+      <c r="AG400" t="n">
+        <v>1030</v>
+      </c>
+      <c r="AH400" t="inlineStr"/>
+      <c r="AI400" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI400"/>
+  <dimension ref="A1:AI401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41012,6 +41012,103 @@
       <c r="AH400" t="inlineStr"/>
       <c r="AI400" t="inlineStr"/>
     </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B401" t="n">
+        <v>835.4299999999999</v>
+      </c>
+      <c r="C401" t="n">
+        <v>900</v>
+      </c>
+      <c r="D401" t="inlineStr"/>
+      <c r="E401" t="n">
+        <v>720</v>
+      </c>
+      <c r="F401" t="n">
+        <v>1408.25</v>
+      </c>
+      <c r="G401" t="n">
+        <v>648.25</v>
+      </c>
+      <c r="H401" t="n">
+        <v>706</v>
+      </c>
+      <c r="I401" t="inlineStr"/>
+      <c r="J401" t="n">
+        <v>605</v>
+      </c>
+      <c r="K401" t="n">
+        <v>1485</v>
+      </c>
+      <c r="L401" t="n">
+        <v>870</v>
+      </c>
+      <c r="M401" t="n">
+        <v>1381</v>
+      </c>
+      <c r="N401" t="n">
+        <v>910</v>
+      </c>
+      <c r="O401" t="n">
+        <v>755</v>
+      </c>
+      <c r="P401" t="n">
+        <v>1475</v>
+      </c>
+      <c r="Q401" t="n">
+        <v>905</v>
+      </c>
+      <c r="R401" t="n">
+        <v>771</v>
+      </c>
+      <c r="S401" t="n">
+        <v>1400</v>
+      </c>
+      <c r="T401" t="n">
+        <v>987.75</v>
+      </c>
+      <c r="U401" t="n">
+        <v>780</v>
+      </c>
+      <c r="V401" t="n">
+        <v>1429.5</v>
+      </c>
+      <c r="W401" t="n">
+        <v>915</v>
+      </c>
+      <c r="X401" t="n">
+        <v>755</v>
+      </c>
+      <c r="Y401" t="n">
+        <v>1480</v>
+      </c>
+      <c r="Z401" t="n">
+        <v>735</v>
+      </c>
+      <c r="AA401" t="inlineStr"/>
+      <c r="AB401" t="inlineStr"/>
+      <c r="AC401" t="n">
+        <v>829</v>
+      </c>
+      <c r="AD401" t="n">
+        <v>644</v>
+      </c>
+      <c r="AE401" t="n">
+        <v>1514</v>
+      </c>
+      <c r="AF401" t="n">
+        <v>999.9400000000001</v>
+      </c>
+      <c r="AG401" t="n">
+        <v>1010</v>
+      </c>
+      <c r="AH401" t="inlineStr"/>
+      <c r="AI401" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI401"/>
+  <dimension ref="A1:AI402"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41109,6 +41109,103 @@
       <c r="AH401" t="inlineStr"/>
       <c r="AI401" t="inlineStr"/>
     </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B402" t="n">
+        <v>810.08</v>
+      </c>
+      <c r="C402" t="n">
+        <v>870</v>
+      </c>
+      <c r="D402" t="inlineStr"/>
+      <c r="E402" t="n">
+        <v>707</v>
+      </c>
+      <c r="F402" t="n">
+        <v>1380</v>
+      </c>
+      <c r="G402" t="n">
+        <v>648.75</v>
+      </c>
+      <c r="H402" t="n">
+        <v>705</v>
+      </c>
+      <c r="I402" t="inlineStr"/>
+      <c r="J402" t="n">
+        <v>604</v>
+      </c>
+      <c r="K402" t="n">
+        <v>1475</v>
+      </c>
+      <c r="L402" t="n">
+        <v>862</v>
+      </c>
+      <c r="M402" t="n">
+        <v>1531</v>
+      </c>
+      <c r="N402" t="n">
+        <v>890</v>
+      </c>
+      <c r="O402" t="n">
+        <v>738</v>
+      </c>
+      <c r="P402" t="n">
+        <v>1435</v>
+      </c>
+      <c r="Q402" t="n">
+        <v>889</v>
+      </c>
+      <c r="R402" t="n">
+        <v>777</v>
+      </c>
+      <c r="S402" t="n">
+        <v>1356</v>
+      </c>
+      <c r="T402" t="n">
+        <v>984</v>
+      </c>
+      <c r="U402" t="n">
+        <v>780</v>
+      </c>
+      <c r="V402" t="n">
+        <v>1408.5</v>
+      </c>
+      <c r="W402" t="n">
+        <v>895</v>
+      </c>
+      <c r="X402" t="n">
+        <v>738</v>
+      </c>
+      <c r="Y402" t="n">
+        <v>1440</v>
+      </c>
+      <c r="Z402" t="n">
+        <v>739</v>
+      </c>
+      <c r="AA402" t="inlineStr"/>
+      <c r="AB402" t="inlineStr"/>
+      <c r="AC402" t="n">
+        <v>839</v>
+      </c>
+      <c r="AD402" t="n">
+        <v>641</v>
+      </c>
+      <c r="AE402" t="n">
+        <v>1534</v>
+      </c>
+      <c r="AF402" t="n">
+        <v>985.04</v>
+      </c>
+      <c r="AG402" t="n">
+        <v>995</v>
+      </c>
+      <c r="AH402" t="inlineStr"/>
+      <c r="AI402" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI402"/>
+  <dimension ref="A1:AI403"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41206,6 +41206,103 @@
       <c r="AH402" t="inlineStr"/>
       <c r="AI402" t="inlineStr"/>
     </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B403" t="n">
+        <v>801.3</v>
+      </c>
+      <c r="C403" t="n">
+        <v>848</v>
+      </c>
+      <c r="D403" t="inlineStr"/>
+      <c r="E403" t="n">
+        <v>710</v>
+      </c>
+      <c r="F403" t="n">
+        <v>1315.25</v>
+      </c>
+      <c r="G403" t="n">
+        <v>621.75</v>
+      </c>
+      <c r="H403" t="n">
+        <v>675</v>
+      </c>
+      <c r="I403" t="inlineStr"/>
+      <c r="J403" t="n">
+        <v>582</v>
+      </c>
+      <c r="K403" t="n">
+        <v>1422</v>
+      </c>
+      <c r="L403" t="n">
+        <v>845</v>
+      </c>
+      <c r="M403" t="n">
+        <v>1631</v>
+      </c>
+      <c r="N403" t="n">
+        <v>915</v>
+      </c>
+      <c r="O403" t="n">
+        <v>750</v>
+      </c>
+      <c r="P403" t="n">
+        <v>1400</v>
+      </c>
+      <c r="Q403" t="n">
+        <v>884</v>
+      </c>
+      <c r="R403" t="n">
+        <v>770</v>
+      </c>
+      <c r="S403" t="n">
+        <v>1315</v>
+      </c>
+      <c r="T403" t="n">
+        <v>986</v>
+      </c>
+      <c r="U403" t="n">
+        <v>805.25</v>
+      </c>
+      <c r="V403" t="n">
+        <v>1386.25</v>
+      </c>
+      <c r="W403" t="n">
+        <v>915</v>
+      </c>
+      <c r="X403" t="n">
+        <v>750</v>
+      </c>
+      <c r="Y403" t="n">
+        <v>1405</v>
+      </c>
+      <c r="Z403" t="n">
+        <v>722</v>
+      </c>
+      <c r="AA403" t="inlineStr"/>
+      <c r="AB403" t="inlineStr"/>
+      <c r="AC403" t="n">
+        <v>814</v>
+      </c>
+      <c r="AD403" t="n">
+        <v>644</v>
+      </c>
+      <c r="AE403" t="n">
+        <v>1514</v>
+      </c>
+      <c r="AF403" t="n">
+        <v>984.9</v>
+      </c>
+      <c r="AG403" t="n">
+        <v>995</v>
+      </c>
+      <c r="AH403" t="inlineStr"/>
+      <c r="AI403" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI403"/>
+  <dimension ref="A1:AI404"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41303,6 +41303,103 @@
       <c r="AH403" t="inlineStr"/>
       <c r="AI403" t="inlineStr"/>
     </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B404" t="n">
+        <v>803.65</v>
+      </c>
+      <c r="C404" t="n">
+        <v>851</v>
+      </c>
+      <c r="D404" t="inlineStr"/>
+      <c r="E404" t="n">
+        <v>705</v>
+      </c>
+      <c r="F404" t="n">
+        <v>1290</v>
+      </c>
+      <c r="G404" t="n">
+        <v>615.25</v>
+      </c>
+      <c r="H404" t="n">
+        <v>665</v>
+      </c>
+      <c r="I404" t="inlineStr"/>
+      <c r="J404" t="n">
+        <v>576</v>
+      </c>
+      <c r="K404" t="n">
+        <v>1395</v>
+      </c>
+      <c r="L404" t="n">
+        <v>829</v>
+      </c>
+      <c r="M404" t="n">
+        <v>1672</v>
+      </c>
+      <c r="N404" t="n">
+        <v>945</v>
+      </c>
+      <c r="O404" t="n">
+        <v>780</v>
+      </c>
+      <c r="P404" t="n">
+        <v>1397</v>
+      </c>
+      <c r="Q404" t="n">
+        <v>888</v>
+      </c>
+      <c r="R404" t="n">
+        <v>778</v>
+      </c>
+      <c r="S404" t="n">
+        <v>1305</v>
+      </c>
+      <c r="T404" t="n">
+        <v>963</v>
+      </c>
+      <c r="U404" t="n">
+        <v>795</v>
+      </c>
+      <c r="V404" t="n">
+        <v>1377</v>
+      </c>
+      <c r="W404" t="n">
+        <v>945</v>
+      </c>
+      <c r="X404" t="n">
+        <v>780</v>
+      </c>
+      <c r="Y404" t="n">
+        <v>1402</v>
+      </c>
+      <c r="Z404" t="n">
+        <v>700</v>
+      </c>
+      <c r="AA404" t="inlineStr"/>
+      <c r="AB404" t="inlineStr"/>
+      <c r="AC404" t="n">
+        <v>809</v>
+      </c>
+      <c r="AD404" t="n">
+        <v>643</v>
+      </c>
+      <c r="AE404" t="n">
+        <v>1509</v>
+      </c>
+      <c r="AF404" t="n">
+        <v>980.26</v>
+      </c>
+      <c r="AG404" t="n">
+        <v>990</v>
+      </c>
+      <c r="AH404" t="inlineStr"/>
+      <c r="AI404" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI404"/>
+  <dimension ref="A1:AI405"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41400,6 +41400,103 @@
       <c r="AH404" t="inlineStr"/>
       <c r="AI404" t="inlineStr"/>
     </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B405" t="n">
+        <v>790.73</v>
+      </c>
+      <c r="C405" t="n">
+        <v>850</v>
+      </c>
+      <c r="D405" t="inlineStr"/>
+      <c r="E405" t="n">
+        <v>680</v>
+      </c>
+      <c r="F405" t="n">
+        <v>1350.5</v>
+      </c>
+      <c r="G405" t="n">
+        <v>630.25</v>
+      </c>
+      <c r="H405" t="n">
+        <v>685</v>
+      </c>
+      <c r="I405" t="inlineStr"/>
+      <c r="J405" t="n">
+        <v>606</v>
+      </c>
+      <c r="K405" t="n">
+        <v>1464</v>
+      </c>
+      <c r="L405" t="n">
+        <v>839</v>
+      </c>
+      <c r="M405" t="n">
+        <v>1678</v>
+      </c>
+      <c r="N405" t="n">
+        <v>950</v>
+      </c>
+      <c r="O405" t="n">
+        <v>820</v>
+      </c>
+      <c r="P405" t="n">
+        <v>1440</v>
+      </c>
+      <c r="Q405" t="n">
+        <v>878</v>
+      </c>
+      <c r="R405" t="n">
+        <v>771</v>
+      </c>
+      <c r="S405" t="n">
+        <v>1340</v>
+      </c>
+      <c r="T405" t="n">
+        <v>925</v>
+      </c>
+      <c r="U405" t="n">
+        <v>803.25</v>
+      </c>
+      <c r="V405" t="n">
+        <v>1407.75</v>
+      </c>
+      <c r="W405" t="n">
+        <v>950</v>
+      </c>
+      <c r="X405" t="n">
+        <v>820</v>
+      </c>
+      <c r="Y405" t="n">
+        <v>1445</v>
+      </c>
+      <c r="Z405" t="n">
+        <v>711</v>
+      </c>
+      <c r="AA405" t="inlineStr"/>
+      <c r="AB405" t="inlineStr"/>
+      <c r="AC405" t="n">
+        <v>814</v>
+      </c>
+      <c r="AD405" t="n">
+        <v>656</v>
+      </c>
+      <c r="AE405" t="n">
+        <v>1474</v>
+      </c>
+      <c r="AF405" t="n">
+        <v>947.05</v>
+      </c>
+      <c r="AG405" t="n">
+        <v>977</v>
+      </c>
+      <c r="AH405" t="inlineStr"/>
+      <c r="AI405" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI405"/>
+  <dimension ref="A1:AI406"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41497,6 +41497,103 @@
       <c r="AH405" t="inlineStr"/>
       <c r="AI405" t="inlineStr"/>
     </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B406" t="n">
+        <v>808.41</v>
+      </c>
+      <c r="C406" t="n">
+        <v>865</v>
+      </c>
+      <c r="D406" t="inlineStr"/>
+      <c r="E406" t="n">
+        <v>745</v>
+      </c>
+      <c r="F406" t="n">
+        <v>1270</v>
+      </c>
+      <c r="G406" t="n">
+        <v>640.25</v>
+      </c>
+      <c r="H406" t="n">
+        <v>689</v>
+      </c>
+      <c r="I406" t="inlineStr"/>
+      <c r="J406" t="n">
+        <v>632</v>
+      </c>
+      <c r="K406" t="n">
+        <v>1404</v>
+      </c>
+      <c r="L406" t="n">
+        <v>843</v>
+      </c>
+      <c r="M406" t="n">
+        <v>1668</v>
+      </c>
+      <c r="N406" t="n">
+        <v>980</v>
+      </c>
+      <c r="O406" t="n">
+        <v>890</v>
+      </c>
+      <c r="P406" t="n">
+        <v>1431</v>
+      </c>
+      <c r="Q406" t="n">
+        <v>919</v>
+      </c>
+      <c r="R406" t="n">
+        <v>862</v>
+      </c>
+      <c r="S406" t="n">
+        <v>1320</v>
+      </c>
+      <c r="T406" t="n">
+        <v>974.25</v>
+      </c>
+      <c r="U406" t="n">
+        <v>833</v>
+      </c>
+      <c r="V406" t="n">
+        <v>1380.25</v>
+      </c>
+      <c r="W406" t="n">
+        <v>980</v>
+      </c>
+      <c r="X406" t="n">
+        <v>890</v>
+      </c>
+      <c r="Y406" t="n">
+        <v>1436</v>
+      </c>
+      <c r="Z406" t="n">
+        <v>724</v>
+      </c>
+      <c r="AA406" t="inlineStr"/>
+      <c r="AB406" t="inlineStr"/>
+      <c r="AC406" t="n">
+        <v>804</v>
+      </c>
+      <c r="AD406" t="n">
+        <v>670</v>
+      </c>
+      <c r="AE406" t="n">
+        <v>1474</v>
+      </c>
+      <c r="AF406" t="n">
+        <v>919.75</v>
+      </c>
+      <c r="AG406" t="n">
+        <v>965</v>
+      </c>
+      <c r="AH406" t="inlineStr"/>
+      <c r="AI406" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI406"/>
+  <dimension ref="A1:AI407"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41500,99 +41500,196 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B406" t="n">
-        <v>808.41</v>
+        <v>821.11</v>
       </c>
       <c r="C406" t="n">
-        <v>865</v>
+        <v>879</v>
       </c>
       <c r="D406" t="inlineStr"/>
       <c r="E406" t="n">
-        <v>745</v>
+        <v>740</v>
       </c>
       <c r="F406" t="n">
-        <v>1270</v>
+        <v>1344.25</v>
       </c>
       <c r="G406" t="n">
-        <v>640.25</v>
+        <v>657.5</v>
       </c>
       <c r="H406" t="n">
-        <v>689</v>
+        <v>706</v>
       </c>
       <c r="I406" t="inlineStr"/>
       <c r="J406" t="n">
-        <v>632</v>
+        <v>640</v>
       </c>
       <c r="K406" t="n">
-        <v>1404</v>
+        <v>1510</v>
       </c>
       <c r="L406" t="n">
-        <v>843</v>
+        <v>853</v>
       </c>
       <c r="M406" t="n">
-        <v>1668</v>
+        <v>1674</v>
       </c>
       <c r="N406" t="n">
-        <v>980</v>
+        <v>1020</v>
       </c>
       <c r="O406" t="n">
         <v>890</v>
       </c>
       <c r="P406" t="n">
-        <v>1431</v>
+        <v>1455</v>
       </c>
       <c r="Q406" t="n">
-        <v>919</v>
+        <v>898</v>
       </c>
       <c r="R406" t="n">
-        <v>862</v>
+        <v>825</v>
       </c>
       <c r="S406" t="n">
-        <v>1320</v>
+        <v>1335</v>
       </c>
       <c r="T406" t="n">
-        <v>974.25</v>
+        <v>965</v>
       </c>
       <c r="U406" t="n">
-        <v>833</v>
+        <v>825</v>
       </c>
       <c r="V406" t="n">
-        <v>1380.25</v>
+        <v>1380</v>
       </c>
       <c r="W406" t="n">
-        <v>980</v>
+        <v>1020</v>
       </c>
       <c r="X406" t="n">
         <v>890</v>
       </c>
       <c r="Y406" t="n">
-        <v>1436</v>
+        <v>1460</v>
       </c>
       <c r="Z406" t="n">
-        <v>724</v>
+        <v>734</v>
       </c>
       <c r="AA406" t="inlineStr"/>
       <c r="AB406" t="inlineStr"/>
       <c r="AC406" t="n">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="AD406" t="n">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="AE406" t="n">
-        <v>1474</v>
+        <v>1479</v>
       </c>
       <c r="AF406" t="n">
-        <v>919.75</v>
+        <v>944.6900000000001</v>
       </c>
       <c r="AG406" t="n">
-        <v>965</v>
+        <v>980</v>
       </c>
       <c r="AH406" t="inlineStr"/>
       <c r="AI406" t="inlineStr"/>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B407" t="n">
+        <v>808.41</v>
+      </c>
+      <c r="C407" t="n">
+        <v>865</v>
+      </c>
+      <c r="D407" t="inlineStr"/>
+      <c r="E407" t="n">
+        <v>745</v>
+      </c>
+      <c r="F407" t="n">
+        <v>1270</v>
+      </c>
+      <c r="G407" t="n">
+        <v>640.25</v>
+      </c>
+      <c r="H407" t="n">
+        <v>689</v>
+      </c>
+      <c r="I407" t="inlineStr"/>
+      <c r="J407" t="n">
+        <v>632</v>
+      </c>
+      <c r="K407" t="n">
+        <v>1404</v>
+      </c>
+      <c r="L407" t="n">
+        <v>843</v>
+      </c>
+      <c r="M407" t="n">
+        <v>1668</v>
+      </c>
+      <c r="N407" t="n">
+        <v>980</v>
+      </c>
+      <c r="O407" t="n">
+        <v>890</v>
+      </c>
+      <c r="P407" t="n">
+        <v>1431</v>
+      </c>
+      <c r="Q407" t="n">
+        <v>919</v>
+      </c>
+      <c r="R407" t="n">
+        <v>862</v>
+      </c>
+      <c r="S407" t="n">
+        <v>1320</v>
+      </c>
+      <c r="T407" t="n">
+        <v>974.25</v>
+      </c>
+      <c r="U407" t="n">
+        <v>833</v>
+      </c>
+      <c r="V407" t="n">
+        <v>1380.25</v>
+      </c>
+      <c r="W407" t="n">
+        <v>980</v>
+      </c>
+      <c r="X407" t="n">
+        <v>890</v>
+      </c>
+      <c r="Y407" t="n">
+        <v>1436</v>
+      </c>
+      <c r="Z407" t="n">
+        <v>724</v>
+      </c>
+      <c r="AA407" t="inlineStr"/>
+      <c r="AB407" t="inlineStr"/>
+      <c r="AC407" t="n">
+        <v>804</v>
+      </c>
+      <c r="AD407" t="n">
+        <v>670</v>
+      </c>
+      <c r="AE407" t="n">
+        <v>1474</v>
+      </c>
+      <c r="AF407" t="n">
+        <v>919.75</v>
+      </c>
+      <c r="AG407" t="n">
+        <v>965</v>
+      </c>
+      <c r="AH407" t="inlineStr"/>
+      <c r="AI407" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI407"/>
+  <dimension ref="A1:AI408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41691,6 +41691,103 @@
       <c r="AH407" t="inlineStr"/>
       <c r="AI407" t="inlineStr"/>
     </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B408" t="n">
+        <v>802.55</v>
+      </c>
+      <c r="C408" t="n">
+        <v>865</v>
+      </c>
+      <c r="D408" t="inlineStr"/>
+      <c r="E408" t="n">
+        <v>748</v>
+      </c>
+      <c r="F408" t="n">
+        <v>1327</v>
+      </c>
+      <c r="G408" t="n">
+        <v>636.75</v>
+      </c>
+      <c r="H408" t="n">
+        <v>698</v>
+      </c>
+      <c r="I408" t="inlineStr"/>
+      <c r="J408" t="n">
+        <v>642</v>
+      </c>
+      <c r="K408" t="n">
+        <v>1406</v>
+      </c>
+      <c r="L408" t="n">
+        <v>837</v>
+      </c>
+      <c r="M408" t="n">
+        <v>1666</v>
+      </c>
+      <c r="N408" t="n">
+        <v>970</v>
+      </c>
+      <c r="O408" t="n">
+        <v>900</v>
+      </c>
+      <c r="P408" t="n">
+        <v>1470</v>
+      </c>
+      <c r="Q408" t="n">
+        <v>919</v>
+      </c>
+      <c r="R408" t="n">
+        <v>868</v>
+      </c>
+      <c r="S408" t="n">
+        <v>1340</v>
+      </c>
+      <c r="T408" t="n">
+        <v>960</v>
+      </c>
+      <c r="U408" t="n">
+        <v>840</v>
+      </c>
+      <c r="V408" t="n">
+        <v>1390.75</v>
+      </c>
+      <c r="W408" t="n">
+        <v>970</v>
+      </c>
+      <c r="X408" t="n">
+        <v>900</v>
+      </c>
+      <c r="Y408" t="n">
+        <v>1475</v>
+      </c>
+      <c r="Z408" t="n">
+        <v>724</v>
+      </c>
+      <c r="AA408" t="inlineStr"/>
+      <c r="AB408" t="inlineStr"/>
+      <c r="AC408" t="n">
+        <v>799</v>
+      </c>
+      <c r="AD408" t="n">
+        <v>666</v>
+      </c>
+      <c r="AE408" t="n">
+        <v>1479</v>
+      </c>
+      <c r="AF408" t="n">
+        <v>934.99</v>
+      </c>
+      <c r="AG408" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH408" t="inlineStr"/>
+      <c r="AI408" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI408"/>
+  <dimension ref="A1:AI409"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41788,6 +41788,103 @@
       <c r="AH408" t="inlineStr"/>
       <c r="AI408" t="inlineStr"/>
     </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B409" t="n">
+        <v>790.9</v>
+      </c>
+      <c r="C409" t="n">
+        <v>855</v>
+      </c>
+      <c r="D409" t="inlineStr"/>
+      <c r="E409" t="n">
+        <v>731</v>
+      </c>
+      <c r="F409" t="n">
+        <v>1240</v>
+      </c>
+      <c r="G409" t="n">
+        <v>614.5</v>
+      </c>
+      <c r="H409" t="n">
+        <v>670</v>
+      </c>
+      <c r="I409" t="inlineStr"/>
+      <c r="J409" t="n">
+        <v>618</v>
+      </c>
+      <c r="K409" t="n">
+        <v>1332</v>
+      </c>
+      <c r="L409" t="n">
+        <v>812</v>
+      </c>
+      <c r="M409" t="n">
+        <v>1664</v>
+      </c>
+      <c r="N409" t="n">
+        <v>938</v>
+      </c>
+      <c r="O409" t="n">
+        <v>875</v>
+      </c>
+      <c r="P409" t="n">
+        <v>1416</v>
+      </c>
+      <c r="Q409" t="n">
+        <v>919</v>
+      </c>
+      <c r="R409" t="n">
+        <v>865</v>
+      </c>
+      <c r="S409" t="n">
+        <v>1295</v>
+      </c>
+      <c r="T409" t="n">
+        <v>948</v>
+      </c>
+      <c r="U409" t="n">
+        <v>840</v>
+      </c>
+      <c r="V409" t="n">
+        <v>1325</v>
+      </c>
+      <c r="W409" t="n">
+        <v>940</v>
+      </c>
+      <c r="X409" t="n">
+        <v>875</v>
+      </c>
+      <c r="Y409" t="n">
+        <v>1421</v>
+      </c>
+      <c r="Z409" t="n">
+        <v>712</v>
+      </c>
+      <c r="AA409" t="inlineStr"/>
+      <c r="AB409" t="inlineStr"/>
+      <c r="AC409" t="n">
+        <v>784</v>
+      </c>
+      <c r="AD409" t="n">
+        <v>659</v>
+      </c>
+      <c r="AE409" t="n">
+        <v>1444</v>
+      </c>
+      <c r="AF409" t="n">
+        <v>914.91</v>
+      </c>
+      <c r="AG409" t="n">
+        <v>950</v>
+      </c>
+      <c r="AH409" t="inlineStr"/>
+      <c r="AI409" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI409"/>
+  <dimension ref="A1:AI410"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41885,6 +41885,103 @@
       <c r="AH409" t="inlineStr"/>
       <c r="AI409" t="inlineStr"/>
     </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B410" t="n">
+        <v>782.85</v>
+      </c>
+      <c r="C410" t="n">
+        <v>848</v>
+      </c>
+      <c r="D410" t="inlineStr"/>
+      <c r="E410" t="n">
+        <v>725</v>
+      </c>
+      <c r="F410" t="n">
+        <v>1275</v>
+      </c>
+      <c r="G410" t="n">
+        <v>633.75</v>
+      </c>
+      <c r="H410" t="n">
+        <v>680</v>
+      </c>
+      <c r="I410" t="inlineStr"/>
+      <c r="J410" t="n">
+        <v>620</v>
+      </c>
+      <c r="K410" t="n">
+        <v>1395</v>
+      </c>
+      <c r="L410" t="n">
+        <v>825</v>
+      </c>
+      <c r="M410" t="n">
+        <v>1663</v>
+      </c>
+      <c r="N410" t="n">
+        <v>915</v>
+      </c>
+      <c r="O410" t="n">
+        <v>868</v>
+      </c>
+      <c r="P410" t="n">
+        <v>1445</v>
+      </c>
+      <c r="Q410" t="n">
+        <v>911</v>
+      </c>
+      <c r="R410" t="n">
+        <v>885</v>
+      </c>
+      <c r="S410" t="n">
+        <v>1310</v>
+      </c>
+      <c r="T410" t="n">
+        <v>940</v>
+      </c>
+      <c r="U410" t="n">
+        <v>855</v>
+      </c>
+      <c r="V410" t="n">
+        <v>1374.25</v>
+      </c>
+      <c r="W410" t="n">
+        <v>917</v>
+      </c>
+      <c r="X410" t="n">
+        <v>868</v>
+      </c>
+      <c r="Y410" t="n">
+        <v>1450</v>
+      </c>
+      <c r="Z410" t="n">
+        <v>707</v>
+      </c>
+      <c r="AA410" t="inlineStr"/>
+      <c r="AB410" t="inlineStr"/>
+      <c r="AC410" t="n">
+        <v>794</v>
+      </c>
+      <c r="AD410" t="n">
+        <v>664</v>
+      </c>
+      <c r="AE410" t="n">
+        <v>1469</v>
+      </c>
+      <c r="AF410" t="n">
+        <v>905.09</v>
+      </c>
+      <c r="AG410" t="n">
+        <v>940</v>
+      </c>
+      <c r="AH410" t="inlineStr"/>
+      <c r="AI410" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI410"/>
+  <dimension ref="A1:AI411"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41982,6 +41982,103 @@
       <c r="AH410" t="inlineStr"/>
       <c r="AI410" t="inlineStr"/>
     </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B411" t="n">
+        <v>820.5</v>
+      </c>
+      <c r="C411" t="n">
+        <v>886</v>
+      </c>
+      <c r="D411" t="inlineStr"/>
+      <c r="E411" t="n">
+        <v>775</v>
+      </c>
+      <c r="F411" t="n">
+        <v>1338.25</v>
+      </c>
+      <c r="G411" t="n">
+        <v>629.75</v>
+      </c>
+      <c r="H411" t="n">
+        <v>685</v>
+      </c>
+      <c r="I411" t="inlineStr"/>
+      <c r="J411" t="n">
+        <v>622</v>
+      </c>
+      <c r="K411" t="n">
+        <v>1396</v>
+      </c>
+      <c r="L411" t="n">
+        <v>858</v>
+      </c>
+      <c r="M411" t="n">
+        <v>1668</v>
+      </c>
+      <c r="N411" t="n">
+        <v>938</v>
+      </c>
+      <c r="O411" t="n">
+        <v>895</v>
+      </c>
+      <c r="P411" t="n">
+        <v>1455</v>
+      </c>
+      <c r="Q411" t="n">
+        <v>930</v>
+      </c>
+      <c r="R411" t="n">
+        <v>925</v>
+      </c>
+      <c r="S411" t="n">
+        <v>1345</v>
+      </c>
+      <c r="T411" t="n">
+        <v>988</v>
+      </c>
+      <c r="U411" t="n">
+        <v>905</v>
+      </c>
+      <c r="V411" t="n">
+        <v>1385</v>
+      </c>
+      <c r="W411" t="n">
+        <v>940</v>
+      </c>
+      <c r="X411" t="n">
+        <v>895</v>
+      </c>
+      <c r="Y411" t="n">
+        <v>1460</v>
+      </c>
+      <c r="Z411" t="n">
+        <v>715</v>
+      </c>
+      <c r="AA411" t="inlineStr"/>
+      <c r="AB411" t="inlineStr"/>
+      <c r="AC411" t="n">
+        <v>799</v>
+      </c>
+      <c r="AD411" t="n">
+        <v>660</v>
+      </c>
+      <c r="AE411" t="n">
+        <v>1464</v>
+      </c>
+      <c r="AF411" t="n">
+        <v>939.88</v>
+      </c>
+      <c r="AG411" t="n">
+        <v>975</v>
+      </c>
+      <c r="AH411" t="inlineStr"/>
+      <c r="AI411" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI411"/>
+  <dimension ref="A1:AI412"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42079,6 +42079,103 @@
       <c r="AH411" t="inlineStr"/>
       <c r="AI411" t="inlineStr"/>
     </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B412" t="n">
+        <v>809.67</v>
+      </c>
+      <c r="C412" t="n">
+        <v>880</v>
+      </c>
+      <c r="D412" t="inlineStr"/>
+      <c r="E412" t="n">
+        <v>775</v>
+      </c>
+      <c r="F412" t="n">
+        <v>1266.75</v>
+      </c>
+      <c r="G412" t="n">
+        <v>611.25</v>
+      </c>
+      <c r="H412" t="n">
+        <v>674</v>
+      </c>
+      <c r="I412" t="inlineStr"/>
+      <c r="J412" t="n">
+        <v>604</v>
+      </c>
+      <c r="K412" t="n">
+        <v>1318</v>
+      </c>
+      <c r="L412" t="n">
+        <v>844</v>
+      </c>
+      <c r="M412" t="n">
+        <v>1662</v>
+      </c>
+      <c r="N412" t="n">
+        <v>928</v>
+      </c>
+      <c r="O412" t="n">
+        <v>886</v>
+      </c>
+      <c r="P412" t="n">
+        <v>1400</v>
+      </c>
+      <c r="Q412" t="n">
+        <v>919</v>
+      </c>
+      <c r="R412" t="n">
+        <v>900</v>
+      </c>
+      <c r="S412" t="n">
+        <v>1300</v>
+      </c>
+      <c r="T412" t="n">
+        <v>977</v>
+      </c>
+      <c r="U412" t="n">
+        <v>903</v>
+      </c>
+      <c r="V412" t="n">
+        <v>1335</v>
+      </c>
+      <c r="W412" t="n">
+        <v>930</v>
+      </c>
+      <c r="X412" t="n">
+        <v>886</v>
+      </c>
+      <c r="Y412" t="n">
+        <v>1405</v>
+      </c>
+      <c r="Z412" t="n">
+        <v>713</v>
+      </c>
+      <c r="AA412" t="inlineStr"/>
+      <c r="AB412" t="inlineStr"/>
+      <c r="AC412" t="n">
+        <v>797</v>
+      </c>
+      <c r="AD412" t="n">
+        <v>659</v>
+      </c>
+      <c r="AE412" t="n">
+        <v>1444</v>
+      </c>
+      <c r="AF412" t="n">
+        <v>924.98</v>
+      </c>
+      <c r="AG412" t="n">
+        <v>960</v>
+      </c>
+      <c r="AH412" t="inlineStr"/>
+      <c r="AI412" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI412"/>
+  <dimension ref="A1:AI413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42176,6 +42176,103 @@
       <c r="AH412" t="inlineStr"/>
       <c r="AI412" t="inlineStr"/>
     </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B413" t="n">
+        <v>832.4299999999999</v>
+      </c>
+      <c r="C413" t="n">
+        <v>899</v>
+      </c>
+      <c r="D413" t="inlineStr"/>
+      <c r="E413" t="n">
+        <v>794</v>
+      </c>
+      <c r="F413" t="n">
+        <v>1225</v>
+      </c>
+      <c r="G413" t="n">
+        <v>620</v>
+      </c>
+      <c r="H413" t="n">
+        <v>665</v>
+      </c>
+      <c r="I413" t="inlineStr"/>
+      <c r="J413" t="n">
+        <v>600</v>
+      </c>
+      <c r="K413" t="n">
+        <v>1276</v>
+      </c>
+      <c r="L413" t="n">
+        <v>870</v>
+      </c>
+      <c r="M413" t="n">
+        <v>1662</v>
+      </c>
+      <c r="N413" t="n">
+        <v>928</v>
+      </c>
+      <c r="O413" t="n">
+        <v>896</v>
+      </c>
+      <c r="P413" t="n">
+        <v>1360</v>
+      </c>
+      <c r="Q413" t="n">
+        <v>943</v>
+      </c>
+      <c r="R413" t="n">
+        <v>913</v>
+      </c>
+      <c r="S413" t="n">
+        <v>1250</v>
+      </c>
+      <c r="T413" t="n">
+        <v>987</v>
+      </c>
+      <c r="U413" t="n">
+        <v>935</v>
+      </c>
+      <c r="V413" t="n">
+        <v>1282</v>
+      </c>
+      <c r="W413" t="n">
+        <v>930</v>
+      </c>
+      <c r="X413" t="n">
+        <v>896</v>
+      </c>
+      <c r="Y413" t="n">
+        <v>1365</v>
+      </c>
+      <c r="Z413" t="n">
+        <v>713</v>
+      </c>
+      <c r="AA413" t="inlineStr"/>
+      <c r="AB413" t="inlineStr"/>
+      <c r="AC413" t="n">
+        <v>824</v>
+      </c>
+      <c r="AD413" t="n">
+        <v>677</v>
+      </c>
+      <c r="AE413" t="n">
+        <v>1452</v>
+      </c>
+      <c r="AF413" t="n">
+        <v>945.04</v>
+      </c>
+      <c r="AG413" t="n">
+        <v>980</v>
+      </c>
+      <c r="AH413" t="inlineStr"/>
+      <c r="AI413" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI413"/>
+  <dimension ref="A1:AI414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42273,6 +42273,103 @@
       <c r="AH413" t="inlineStr"/>
       <c r="AI413" t="inlineStr"/>
     </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B414" t="n">
+        <v>830.15</v>
+      </c>
+      <c r="C414" t="n">
+        <v>897</v>
+      </c>
+      <c r="D414" t="inlineStr"/>
+      <c r="E414" t="n">
+        <v>805</v>
+      </c>
+      <c r="F414" t="n">
+        <v>1238</v>
+      </c>
+      <c r="G414" t="n">
+        <v>640.5</v>
+      </c>
+      <c r="H414" t="n">
+        <v>695</v>
+      </c>
+      <c r="I414" t="inlineStr"/>
+      <c r="J414" t="n">
+        <v>622</v>
+      </c>
+      <c r="K414" t="n">
+        <v>1352</v>
+      </c>
+      <c r="L414" t="n">
+        <v>865</v>
+      </c>
+      <c r="M414" t="n">
+        <v>1695</v>
+      </c>
+      <c r="N414" t="n">
+        <v>920</v>
+      </c>
+      <c r="O414" t="n">
+        <v>892</v>
+      </c>
+      <c r="P414" t="n">
+        <v>1365</v>
+      </c>
+      <c r="Q414" t="n">
+        <v>943</v>
+      </c>
+      <c r="R414" t="n">
+        <v>918</v>
+      </c>
+      <c r="S414" t="n">
+        <v>1273</v>
+      </c>
+      <c r="T414" t="n">
+        <v>990</v>
+      </c>
+      <c r="U414" t="n">
+        <v>940</v>
+      </c>
+      <c r="V414" t="n">
+        <v>1300</v>
+      </c>
+      <c r="W414" t="n">
+        <v>922</v>
+      </c>
+      <c r="X414" t="n">
+        <v>892</v>
+      </c>
+      <c r="Y414" t="n">
+        <v>1370</v>
+      </c>
+      <c r="Z414" t="n">
+        <v>717</v>
+      </c>
+      <c r="AA414" t="inlineStr"/>
+      <c r="AB414" t="inlineStr"/>
+      <c r="AC414" t="n">
+        <v>819</v>
+      </c>
+      <c r="AD414" t="n">
+        <v>682</v>
+      </c>
+      <c r="AE414" t="n">
+        <v>1454</v>
+      </c>
+      <c r="AF414" t="n">
+        <v>939.79</v>
+      </c>
+      <c r="AG414" t="n">
+        <v>975</v>
+      </c>
+      <c r="AH414" t="inlineStr"/>
+      <c r="AI414" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI414"/>
+  <dimension ref="A1:AI415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42370,6 +42370,103 @@
       <c r="AH414" t="inlineStr"/>
       <c r="AI414" t="inlineStr"/>
     </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B415" t="n">
+        <v>825.54</v>
+      </c>
+      <c r="C415" t="n">
+        <v>892</v>
+      </c>
+      <c r="D415" t="inlineStr"/>
+      <c r="E415" t="n">
+        <v>818</v>
+      </c>
+      <c r="F415" t="n">
+        <v>1330.75</v>
+      </c>
+      <c r="G415" t="n">
+        <v>673.5</v>
+      </c>
+      <c r="H415" t="n">
+        <v>720</v>
+      </c>
+      <c r="I415" t="inlineStr"/>
+      <c r="J415" t="n">
+        <v>655</v>
+      </c>
+      <c r="K415" t="n">
+        <v>1420</v>
+      </c>
+      <c r="L415" t="n">
+        <v>862</v>
+      </c>
+      <c r="M415" t="n">
+        <v>1697</v>
+      </c>
+      <c r="N415" t="n">
+        <v>915</v>
+      </c>
+      <c r="O415" t="n">
+        <v>893</v>
+      </c>
+      <c r="P415" t="n">
+        <v>1405</v>
+      </c>
+      <c r="Q415" t="n">
+        <v>938</v>
+      </c>
+      <c r="R415" t="n">
+        <v>919</v>
+      </c>
+      <c r="S415" t="n">
+        <v>1323</v>
+      </c>
+      <c r="T415" t="n">
+        <v>996</v>
+      </c>
+      <c r="U415" t="n">
+        <v>960</v>
+      </c>
+      <c r="V415" t="n">
+        <v>1350</v>
+      </c>
+      <c r="W415" t="n">
+        <v>917</v>
+      </c>
+      <c r="X415" t="n">
+        <v>893</v>
+      </c>
+      <c r="Y415" t="n">
+        <v>1410</v>
+      </c>
+      <c r="Z415" t="n">
+        <v>747</v>
+      </c>
+      <c r="AA415" t="inlineStr"/>
+      <c r="AB415" t="inlineStr"/>
+      <c r="AC415" t="n">
+        <v>854</v>
+      </c>
+      <c r="AD415" t="n">
+        <v>707</v>
+      </c>
+      <c r="AE415" t="n">
+        <v>1469</v>
+      </c>
+      <c r="AF415" t="n">
+        <v>934.96</v>
+      </c>
+      <c r="AG415" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH415" t="inlineStr"/>
+      <c r="AI415" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI415"/>
+  <dimension ref="A1:AI416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42467,6 +42467,103 @@
       <c r="AH415" t="inlineStr"/>
       <c r="AI415" t="inlineStr"/>
     </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B416" t="n">
+        <v>814.49</v>
+      </c>
+      <c r="C416" t="n">
+        <v>881</v>
+      </c>
+      <c r="D416" t="inlineStr"/>
+      <c r="E416" t="n">
+        <v>814</v>
+      </c>
+      <c r="F416" t="n">
+        <v>1255</v>
+      </c>
+      <c r="G416" t="n">
+        <v>668.25</v>
+      </c>
+      <c r="H416" t="n">
+        <v>733</v>
+      </c>
+      <c r="I416" t="inlineStr"/>
+      <c r="J416" t="n">
+        <v>660</v>
+      </c>
+      <c r="K416" t="n">
+        <v>1397</v>
+      </c>
+      <c r="L416" t="n">
+        <v>872</v>
+      </c>
+      <c r="M416" t="n">
+        <v>1690</v>
+      </c>
+      <c r="N416" t="n">
+        <v>913</v>
+      </c>
+      <c r="O416" t="n">
+        <v>887</v>
+      </c>
+      <c r="P416" t="n">
+        <v>1380</v>
+      </c>
+      <c r="Q416" t="n">
+        <v>936</v>
+      </c>
+      <c r="R416" t="n">
+        <v>934</v>
+      </c>
+      <c r="S416" t="n">
+        <v>1283</v>
+      </c>
+      <c r="T416" t="n">
+        <v>990</v>
+      </c>
+      <c r="U416" t="n">
+        <v>957</v>
+      </c>
+      <c r="V416" t="n">
+        <v>1305</v>
+      </c>
+      <c r="W416" t="n">
+        <v>915</v>
+      </c>
+      <c r="X416" t="n">
+        <v>887</v>
+      </c>
+      <c r="Y416" t="n">
+        <v>1385</v>
+      </c>
+      <c r="Z416" t="n">
+        <v>732</v>
+      </c>
+      <c r="AA416" t="inlineStr"/>
+      <c r="AB416" t="inlineStr"/>
+      <c r="AC416" t="n">
+        <v>884</v>
+      </c>
+      <c r="AD416" t="n">
+        <v>784</v>
+      </c>
+      <c r="AE416" t="n">
+        <v>1494</v>
+      </c>
+      <c r="AF416" t="n">
+        <v>921.84</v>
+      </c>
+      <c r="AG416" t="n">
+        <v>957</v>
+      </c>
+      <c r="AH416" t="inlineStr"/>
+      <c r="AI416" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI416"/>
+  <dimension ref="A1:AI417"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42179,96 +42179,96 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B413" t="n">
-        <v>832.4299999999999</v>
+        <v>824.61</v>
       </c>
       <c r="C413" t="n">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="D413" t="inlineStr"/>
       <c r="E413" t="n">
-        <v>794</v>
+        <v>790</v>
       </c>
       <c r="F413" t="n">
-        <v>1225</v>
+        <v>1263</v>
       </c>
       <c r="G413" t="n">
-        <v>620</v>
+        <v>622.5</v>
       </c>
       <c r="H413" t="n">
-        <v>665</v>
+        <v>683</v>
       </c>
       <c r="I413" t="inlineStr"/>
       <c r="J413" t="n">
-        <v>600</v>
+        <v>610</v>
       </c>
       <c r="K413" t="n">
-        <v>1276</v>
+        <v>1320</v>
       </c>
       <c r="L413" t="n">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="M413" t="n">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="N413" t="n">
-        <v>928</v>
+        <v>933</v>
       </c>
       <c r="O413" t="n">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="P413" t="n">
-        <v>1360</v>
+        <v>1390</v>
       </c>
       <c r="Q413" t="n">
-        <v>943</v>
+        <v>934</v>
       </c>
       <c r="R413" t="n">
-        <v>913</v>
+        <v>898</v>
       </c>
       <c r="S413" t="n">
-        <v>1250</v>
+        <v>1280</v>
       </c>
       <c r="T413" t="n">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="U413" t="n">
+        <v>925</v>
+      </c>
+      <c r="V413" t="n">
+        <v>1320</v>
+      </c>
+      <c r="W413" t="n">
         <v>935</v>
       </c>
-      <c r="V413" t="n">
-        <v>1282</v>
-      </c>
-      <c r="W413" t="n">
-        <v>930</v>
-      </c>
       <c r="X413" t="n">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="Y413" t="n">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="Z413" t="n">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="AA413" t="inlineStr"/>
       <c r="AB413" t="inlineStr"/>
       <c r="AC413" t="n">
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="AD413" t="n">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="AE413" t="n">
-        <v>1452</v>
+        <v>1449</v>
       </c>
       <c r="AF413" t="n">
-        <v>945.04</v>
+        <v>937.8</v>
       </c>
       <c r="AG413" t="n">
-        <v>980</v>
+        <v>973</v>
       </c>
       <c r="AH413" t="inlineStr"/>
       <c r="AI413" t="inlineStr"/>
@@ -42276,96 +42276,96 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B414" t="n">
-        <v>830.15</v>
+        <v>832.4299999999999</v>
       </c>
       <c r="C414" t="n">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="D414" t="inlineStr"/>
       <c r="E414" t="n">
-        <v>805</v>
+        <v>794</v>
       </c>
       <c r="F414" t="n">
-        <v>1238</v>
+        <v>1225</v>
       </c>
       <c r="G414" t="n">
-        <v>640.5</v>
+        <v>620</v>
       </c>
       <c r="H414" t="n">
-        <v>695</v>
+        <v>665</v>
       </c>
       <c r="I414" t="inlineStr"/>
       <c r="J414" t="n">
-        <v>622</v>
+        <v>600</v>
       </c>
       <c r="K414" t="n">
-        <v>1352</v>
+        <v>1276</v>
       </c>
       <c r="L414" t="n">
-        <v>865</v>
+        <v>870</v>
       </c>
       <c r="M414" t="n">
-        <v>1695</v>
+        <v>1662</v>
       </c>
       <c r="N414" t="n">
-        <v>920</v>
+        <v>928</v>
       </c>
       <c r="O414" t="n">
-        <v>892</v>
+        <v>896</v>
       </c>
       <c r="P414" t="n">
-        <v>1365</v>
+        <v>1360</v>
       </c>
       <c r="Q414" t="n">
         <v>943</v>
       </c>
       <c r="R414" t="n">
-        <v>918</v>
+        <v>913</v>
       </c>
       <c r="S414" t="n">
-        <v>1273</v>
+        <v>1250</v>
       </c>
       <c r="T414" t="n">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="U414" t="n">
-        <v>940</v>
+        <v>935</v>
       </c>
       <c r="V414" t="n">
-        <v>1300</v>
+        <v>1282</v>
       </c>
       <c r="W414" t="n">
-        <v>922</v>
+        <v>930</v>
       </c>
       <c r="X414" t="n">
-        <v>892</v>
+        <v>896</v>
       </c>
       <c r="Y414" t="n">
-        <v>1370</v>
+        <v>1365</v>
       </c>
       <c r="Z414" t="n">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="AA414" t="inlineStr"/>
       <c r="AB414" t="inlineStr"/>
       <c r="AC414" t="n">
-        <v>819</v>
+        <v>824</v>
       </c>
       <c r="AD414" t="n">
-        <v>682</v>
+        <v>677</v>
       </c>
       <c r="AE414" t="n">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="AF414" t="n">
-        <v>939.79</v>
+        <v>945.04</v>
       </c>
       <c r="AG414" t="n">
-        <v>975</v>
+        <v>980</v>
       </c>
       <c r="AH414" t="inlineStr"/>
       <c r="AI414" t="inlineStr"/>
@@ -42373,96 +42373,96 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B415" t="n">
-        <v>825.54</v>
+        <v>830.15</v>
       </c>
       <c r="C415" t="n">
-        <v>892</v>
+        <v>897</v>
       </c>
       <c r="D415" t="inlineStr"/>
       <c r="E415" t="n">
-        <v>818</v>
+        <v>805</v>
       </c>
       <c r="F415" t="n">
-        <v>1330.75</v>
+        <v>1238</v>
       </c>
       <c r="G415" t="n">
-        <v>673.5</v>
+        <v>640.5</v>
       </c>
       <c r="H415" t="n">
-        <v>720</v>
+        <v>695</v>
       </c>
       <c r="I415" t="inlineStr"/>
       <c r="J415" t="n">
-        <v>655</v>
+        <v>622</v>
       </c>
       <c r="K415" t="n">
-        <v>1420</v>
+        <v>1352</v>
       </c>
       <c r="L415" t="n">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="M415" t="n">
-        <v>1697</v>
+        <v>1695</v>
       </c>
       <c r="N415" t="n">
-        <v>915</v>
+        <v>920</v>
       </c>
       <c r="O415" t="n">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="P415" t="n">
-        <v>1405</v>
+        <v>1365</v>
       </c>
       <c r="Q415" t="n">
-        <v>938</v>
+        <v>943</v>
       </c>
       <c r="R415" t="n">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="S415" t="n">
-        <v>1323</v>
+        <v>1273</v>
       </c>
       <c r="T415" t="n">
-        <v>996</v>
+        <v>990</v>
       </c>
       <c r="U415" t="n">
-        <v>960</v>
+        <v>940</v>
       </c>
       <c r="V415" t="n">
-        <v>1350</v>
+        <v>1300</v>
       </c>
       <c r="W415" t="n">
-        <v>917</v>
+        <v>922</v>
       </c>
       <c r="X415" t="n">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="Y415" t="n">
-        <v>1410</v>
+        <v>1370</v>
       </c>
       <c r="Z415" t="n">
-        <v>747</v>
+        <v>717</v>
       </c>
       <c r="AA415" t="inlineStr"/>
       <c r="AB415" t="inlineStr"/>
       <c r="AC415" t="n">
-        <v>854</v>
+        <v>819</v>
       </c>
       <c r="AD415" t="n">
-        <v>707</v>
+        <v>682</v>
       </c>
       <c r="AE415" t="n">
-        <v>1469</v>
+        <v>1454</v>
       </c>
       <c r="AF415" t="n">
-        <v>934.96</v>
+        <v>939.79</v>
       </c>
       <c r="AG415" t="n">
-        <v>970</v>
+        <v>975</v>
       </c>
       <c r="AH415" t="inlineStr"/>
       <c r="AI415" t="inlineStr"/>
@@ -42470,99 +42470,196 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B416" t="n">
-        <v>814.49</v>
+        <v>825.54</v>
       </c>
       <c r="C416" t="n">
-        <v>881</v>
+        <v>892</v>
       </c>
       <c r="D416" t="inlineStr"/>
       <c r="E416" t="n">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="F416" t="n">
-        <v>1255</v>
+        <v>1330.75</v>
       </c>
       <c r="G416" t="n">
-        <v>668.25</v>
+        <v>673.5</v>
       </c>
       <c r="H416" t="n">
-        <v>733</v>
+        <v>720</v>
       </c>
       <c r="I416" t="inlineStr"/>
       <c r="J416" t="n">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="K416" t="n">
-        <v>1397</v>
+        <v>1420</v>
       </c>
       <c r="L416" t="n">
-        <v>872</v>
+        <v>862</v>
       </c>
       <c r="M416" t="n">
-        <v>1690</v>
+        <v>1697</v>
       </c>
       <c r="N416" t="n">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="O416" t="n">
-        <v>887</v>
+        <v>893</v>
       </c>
       <c r="P416" t="n">
-        <v>1380</v>
+        <v>1405</v>
       </c>
       <c r="Q416" t="n">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="R416" t="n">
-        <v>934</v>
+        <v>919</v>
       </c>
       <c r="S416" t="n">
-        <v>1283</v>
+        <v>1323</v>
       </c>
       <c r="T416" t="n">
-        <v>990</v>
+        <v>996</v>
       </c>
       <c r="U416" t="n">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="V416" t="n">
-        <v>1305</v>
+        <v>1350</v>
       </c>
       <c r="W416" t="n">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="X416" t="n">
-        <v>887</v>
+        <v>893</v>
       </c>
       <c r="Y416" t="n">
-        <v>1385</v>
+        <v>1410</v>
       </c>
       <c r="Z416" t="n">
-        <v>732</v>
+        <v>747</v>
       </c>
       <c r="AA416" t="inlineStr"/>
       <c r="AB416" t="inlineStr"/>
       <c r="AC416" t="n">
-        <v>884</v>
+        <v>854</v>
       </c>
       <c r="AD416" t="n">
-        <v>784</v>
+        <v>707</v>
       </c>
       <c r="AE416" t="n">
-        <v>1494</v>
+        <v>1469</v>
       </c>
       <c r="AF416" t="n">
-        <v>921.84</v>
+        <v>934.96</v>
       </c>
       <c r="AG416" t="n">
-        <v>957</v>
+        <v>970</v>
       </c>
       <c r="AH416" t="inlineStr"/>
       <c r="AI416" t="inlineStr"/>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B417" t="n">
+        <v>814.49</v>
+      </c>
+      <c r="C417" t="n">
+        <v>881</v>
+      </c>
+      <c r="D417" t="inlineStr"/>
+      <c r="E417" t="n">
+        <v>814</v>
+      </c>
+      <c r="F417" t="n">
+        <v>1255</v>
+      </c>
+      <c r="G417" t="n">
+        <v>668.25</v>
+      </c>
+      <c r="H417" t="n">
+        <v>733</v>
+      </c>
+      <c r="I417" t="inlineStr"/>
+      <c r="J417" t="n">
+        <v>660</v>
+      </c>
+      <c r="K417" t="n">
+        <v>1397</v>
+      </c>
+      <c r="L417" t="n">
+        <v>872</v>
+      </c>
+      <c r="M417" t="n">
+        <v>1690</v>
+      </c>
+      <c r="N417" t="n">
+        <v>913</v>
+      </c>
+      <c r="O417" t="n">
+        <v>887</v>
+      </c>
+      <c r="P417" t="n">
+        <v>1380</v>
+      </c>
+      <c r="Q417" t="n">
+        <v>936</v>
+      </c>
+      <c r="R417" t="n">
+        <v>934</v>
+      </c>
+      <c r="S417" t="n">
+        <v>1283</v>
+      </c>
+      <c r="T417" t="n">
+        <v>990</v>
+      </c>
+      <c r="U417" t="n">
+        <v>957</v>
+      </c>
+      <c r="V417" t="n">
+        <v>1305</v>
+      </c>
+      <c r="W417" t="n">
+        <v>915</v>
+      </c>
+      <c r="X417" t="n">
+        <v>887</v>
+      </c>
+      <c r="Y417" t="n">
+        <v>1385</v>
+      </c>
+      <c r="Z417" t="n">
+        <v>732</v>
+      </c>
+      <c r="AA417" t="inlineStr"/>
+      <c r="AB417" t="inlineStr"/>
+      <c r="AC417" t="n">
+        <v>884</v>
+      </c>
+      <c r="AD417" t="n">
+        <v>784</v>
+      </c>
+      <c r="AE417" t="n">
+        <v>1494</v>
+      </c>
+      <c r="AF417" t="n">
+        <v>921.84</v>
+      </c>
+      <c r="AG417" t="n">
+        <v>957</v>
+      </c>
+      <c r="AH417" t="inlineStr"/>
+      <c r="AI417" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI417"/>
+  <dimension ref="A1:AI418"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42661,6 +42661,103 @@
       <c r="AH417" t="inlineStr"/>
       <c r="AI417" t="inlineStr"/>
     </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B418" t="n">
+        <v>831.97</v>
+      </c>
+      <c r="C418" t="n">
+        <v>898</v>
+      </c>
+      <c r="D418" t="inlineStr"/>
+      <c r="E418" t="n">
+        <v>838</v>
+      </c>
+      <c r="F418" t="n">
+        <v>1262</v>
+      </c>
+      <c r="G418" t="n">
+        <v>679.25</v>
+      </c>
+      <c r="H418" t="n">
+        <v>750</v>
+      </c>
+      <c r="I418" t="inlineStr"/>
+      <c r="J418" t="n">
+        <v>680</v>
+      </c>
+      <c r="K418" t="n">
+        <v>1365</v>
+      </c>
+      <c r="L418" t="n">
+        <v>878</v>
+      </c>
+      <c r="M418" t="n">
+        <v>1687</v>
+      </c>
+      <c r="N418" t="n">
+        <v>925</v>
+      </c>
+      <c r="O418" t="n">
+        <v>887</v>
+      </c>
+      <c r="P418" t="n">
+        <v>1363</v>
+      </c>
+      <c r="Q418" t="n">
+        <v>938</v>
+      </c>
+      <c r="R418" t="n">
+        <v>936</v>
+      </c>
+      <c r="S418" t="n">
+        <v>1263</v>
+      </c>
+      <c r="T418" t="n">
+        <v>1003</v>
+      </c>
+      <c r="U418" t="n">
+        <v>993</v>
+      </c>
+      <c r="V418" t="n">
+        <v>1320</v>
+      </c>
+      <c r="W418" t="n">
+        <v>930</v>
+      </c>
+      <c r="X418" t="n">
+        <v>887</v>
+      </c>
+      <c r="Y418" t="n">
+        <v>1368</v>
+      </c>
+      <c r="Z418" t="n">
+        <v>730</v>
+      </c>
+      <c r="AA418" t="inlineStr"/>
+      <c r="AB418" t="inlineStr"/>
+      <c r="AC418" t="n">
+        <v>889</v>
+      </c>
+      <c r="AD418" t="n">
+        <v>794</v>
+      </c>
+      <c r="AE418" t="n">
+        <v>1514</v>
+      </c>
+      <c r="AF418" t="n">
+        <v>904.03</v>
+      </c>
+      <c r="AG418" t="n">
+        <v>974</v>
+      </c>
+      <c r="AH418" t="inlineStr"/>
+      <c r="AI418" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI418"/>
+  <dimension ref="A1:AI419"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42758,6 +42758,103 @@
       <c r="AH418" t="inlineStr"/>
       <c r="AI418" t="inlineStr"/>
     </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B419" t="n">
+        <v>853.17</v>
+      </c>
+      <c r="C419" t="n">
+        <v>917</v>
+      </c>
+      <c r="D419" t="inlineStr"/>
+      <c r="E419" t="n">
+        <v>850</v>
+      </c>
+      <c r="F419" t="n">
+        <v>1255</v>
+      </c>
+      <c r="G419" t="n">
+        <v>671.75</v>
+      </c>
+      <c r="H419" t="n">
+        <v>720</v>
+      </c>
+      <c r="I419" t="inlineStr"/>
+      <c r="J419" t="n">
+        <v>640</v>
+      </c>
+      <c r="K419" t="n">
+        <v>1363</v>
+      </c>
+      <c r="L419" t="n">
+        <v>881</v>
+      </c>
+      <c r="M419" t="n">
+        <v>1697</v>
+      </c>
+      <c r="N419" t="n">
+        <v>937</v>
+      </c>
+      <c r="O419" t="n">
+        <v>873</v>
+      </c>
+      <c r="P419" t="n">
+        <v>1378</v>
+      </c>
+      <c r="Q419" t="n">
+        <v>940</v>
+      </c>
+      <c r="R419" t="n">
+        <v>920</v>
+      </c>
+      <c r="S419" t="n">
+        <v>1278</v>
+      </c>
+      <c r="T419" t="n">
+        <v>1035</v>
+      </c>
+      <c r="U419" t="n">
+        <v>1003</v>
+      </c>
+      <c r="V419" t="n">
+        <v>1330</v>
+      </c>
+      <c r="W419" t="n">
+        <v>942</v>
+      </c>
+      <c r="X419" t="n">
+        <v>873</v>
+      </c>
+      <c r="Y419" t="n">
+        <v>1383</v>
+      </c>
+      <c r="Z419" t="n">
+        <v>732</v>
+      </c>
+      <c r="AA419" t="inlineStr"/>
+      <c r="AB419" t="inlineStr"/>
+      <c r="AC419" t="n">
+        <v>881</v>
+      </c>
+      <c r="AD419" t="n">
+        <v>796</v>
+      </c>
+      <c r="AE419" t="n">
+        <v>1499</v>
+      </c>
+      <c r="AF419" t="n">
+        <v>923.0599999999999</v>
+      </c>
+      <c r="AG419" t="n">
+        <v>993</v>
+      </c>
+      <c r="AH419" t="inlineStr"/>
+      <c r="AI419" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI419"/>
+  <dimension ref="A1:AI420"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42855,6 +42855,103 @@
       <c r="AH419" t="inlineStr"/>
       <c r="AI419" t="inlineStr"/>
     </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B420" t="n">
+        <v>845.23</v>
+      </c>
+      <c r="C420" t="n">
+        <v>909</v>
+      </c>
+      <c r="D420" t="inlineStr"/>
+      <c r="E420" t="n">
+        <v>882</v>
+      </c>
+      <c r="F420" t="n">
+        <v>1317.5</v>
+      </c>
+      <c r="G420" t="n">
+        <v>681</v>
+      </c>
+      <c r="H420" t="n">
+        <v>732</v>
+      </c>
+      <c r="I420" t="inlineStr"/>
+      <c r="J420" t="n">
+        <v>655</v>
+      </c>
+      <c r="K420" t="n">
+        <v>1390</v>
+      </c>
+      <c r="L420" t="n">
+        <v>880</v>
+      </c>
+      <c r="M420" t="n">
+        <v>1694</v>
+      </c>
+      <c r="N420" t="n">
+        <v>926</v>
+      </c>
+      <c r="O420" t="n">
+        <v>875</v>
+      </c>
+      <c r="P420" t="n">
+        <v>1405</v>
+      </c>
+      <c r="Q420" t="n">
+        <v>946</v>
+      </c>
+      <c r="R420" t="n">
+        <v>945</v>
+      </c>
+      <c r="S420" t="n">
+        <v>1295</v>
+      </c>
+      <c r="T420" t="n">
+        <v>1050</v>
+      </c>
+      <c r="U420" t="n">
+        <v>1000</v>
+      </c>
+      <c r="V420" t="n">
+        <v>1360</v>
+      </c>
+      <c r="W420" t="n">
+        <v>931</v>
+      </c>
+      <c r="X420" t="n">
+        <v>875</v>
+      </c>
+      <c r="Y420" t="n">
+        <v>1410</v>
+      </c>
+      <c r="Z420" t="n">
+        <v>740</v>
+      </c>
+      <c r="AA420" t="inlineStr"/>
+      <c r="AB420" t="inlineStr"/>
+      <c r="AC420" t="n">
+        <v>888</v>
+      </c>
+      <c r="AD420" t="n">
+        <v>801</v>
+      </c>
+      <c r="AE420" t="n">
+        <v>1497</v>
+      </c>
+      <c r="AF420" t="n">
+        <v>909.99</v>
+      </c>
+      <c r="AG420" t="n">
+        <v>975</v>
+      </c>
+      <c r="AH420" t="inlineStr"/>
+      <c r="AI420" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI420"/>
+  <dimension ref="A1:AI421"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42952,6 +42952,103 @@
       <c r="AH420" t="inlineStr"/>
       <c r="AI420" t="inlineStr"/>
     </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B421" t="n">
+        <v>842.55</v>
+      </c>
+      <c r="C421" t="n">
+        <v>905</v>
+      </c>
+      <c r="D421" t="inlineStr"/>
+      <c r="E421" t="n">
+        <v>889</v>
+      </c>
+      <c r="F421" t="n">
+        <v>1255</v>
+      </c>
+      <c r="G421" t="n">
+        <v>684.75</v>
+      </c>
+      <c r="H421" t="n">
+        <v>730</v>
+      </c>
+      <c r="I421" t="inlineStr"/>
+      <c r="J421" t="n">
+        <v>630</v>
+      </c>
+      <c r="K421" t="n">
+        <v>1380</v>
+      </c>
+      <c r="L421" t="n">
+        <v>875</v>
+      </c>
+      <c r="M421" t="n">
+        <v>1689</v>
+      </c>
+      <c r="N421" t="n">
+        <v>920</v>
+      </c>
+      <c r="O421" t="n">
+        <v>868</v>
+      </c>
+      <c r="P421" t="n">
+        <v>1360</v>
+      </c>
+      <c r="Q421" t="n">
+        <v>930</v>
+      </c>
+      <c r="R421" t="n">
+        <v>920</v>
+      </c>
+      <c r="S421" t="n">
+        <v>1275</v>
+      </c>
+      <c r="T421" t="n">
+        <v>1052</v>
+      </c>
+      <c r="U421" t="n">
+        <v>1004</v>
+      </c>
+      <c r="V421" t="n">
+        <v>1330</v>
+      </c>
+      <c r="W421" t="n">
+        <v>925</v>
+      </c>
+      <c r="X421" t="n">
+        <v>868</v>
+      </c>
+      <c r="Y421" t="n">
+        <v>1365</v>
+      </c>
+      <c r="Z421" t="n">
+        <v>745</v>
+      </c>
+      <c r="AA421" t="inlineStr"/>
+      <c r="AB421" t="inlineStr"/>
+      <c r="AC421" t="n">
+        <v>892</v>
+      </c>
+      <c r="AD421" t="n">
+        <v>804</v>
+      </c>
+      <c r="AE421" t="n">
+        <v>1477</v>
+      </c>
+      <c r="AF421" t="n">
+        <v>904.01</v>
+      </c>
+      <c r="AG421" t="n">
+        <v>964</v>
+      </c>
+      <c r="AH421" t="inlineStr"/>
+      <c r="AI421" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI421"/>
+  <dimension ref="A1:AI422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43049,6 +43049,103 @@
       <c r="AH421" t="inlineStr"/>
       <c r="AI421" t="inlineStr"/>
     </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B422" t="n">
+        <v>849.0700000000001</v>
+      </c>
+      <c r="C422" t="n">
+        <v>910</v>
+      </c>
+      <c r="D422" t="inlineStr"/>
+      <c r="E422" t="n">
+        <v>885</v>
+      </c>
+      <c r="F422" t="n">
+        <v>1250</v>
+      </c>
+      <c r="G422" t="n">
+        <v>691</v>
+      </c>
+      <c r="H422" t="n">
+        <v>740</v>
+      </c>
+      <c r="I422" t="inlineStr"/>
+      <c r="J422" t="n">
+        <v>661</v>
+      </c>
+      <c r="K422" t="n">
+        <v>1366</v>
+      </c>
+      <c r="L422" t="n">
+        <v>878</v>
+      </c>
+      <c r="M422" t="n">
+        <v>1687</v>
+      </c>
+      <c r="N422" t="n">
+        <v>926</v>
+      </c>
+      <c r="O422" t="n">
+        <v>868</v>
+      </c>
+      <c r="P422" t="n">
+        <v>1355</v>
+      </c>
+      <c r="Q422" t="n">
+        <v>935</v>
+      </c>
+      <c r="R422" t="n">
+        <v>922</v>
+      </c>
+      <c r="S422" t="n">
+        <v>1265</v>
+      </c>
+      <c r="T422" t="n">
+        <v>1065</v>
+      </c>
+      <c r="U422" t="n">
+        <v>1000</v>
+      </c>
+      <c r="V422" t="n">
+        <v>1330</v>
+      </c>
+      <c r="W422" t="n">
+        <v>931</v>
+      </c>
+      <c r="X422" t="n">
+        <v>868</v>
+      </c>
+      <c r="Y422" t="n">
+        <v>1360</v>
+      </c>
+      <c r="Z422" t="n">
+        <v>755</v>
+      </c>
+      <c r="AA422" t="inlineStr"/>
+      <c r="AB422" t="inlineStr"/>
+      <c r="AC422" t="n">
+        <v>879</v>
+      </c>
+      <c r="AD422" t="n">
+        <v>821</v>
+      </c>
+      <c r="AE422" t="n">
+        <v>1444</v>
+      </c>
+      <c r="AF422" t="n">
+        <v>903</v>
+      </c>
+      <c r="AG422" t="n">
+        <v>963</v>
+      </c>
+      <c r="AH422" t="inlineStr"/>
+      <c r="AI422" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI422"/>
+  <dimension ref="A1:AI423"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43146,6 +43146,103 @@
       <c r="AH422" t="inlineStr"/>
       <c r="AI422" t="inlineStr"/>
     </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B423" t="n">
+        <v>851.37</v>
+      </c>
+      <c r="C423" t="n">
+        <v>915</v>
+      </c>
+      <c r="D423" t="inlineStr"/>
+      <c r="E423" t="n">
+        <v>888</v>
+      </c>
+      <c r="F423" t="n">
+        <v>1272</v>
+      </c>
+      <c r="G423" t="n">
+        <v>688</v>
+      </c>
+      <c r="H423" t="n">
+        <v>745</v>
+      </c>
+      <c r="I423" t="inlineStr"/>
+      <c r="J423" t="n">
+        <v>670</v>
+      </c>
+      <c r="K423" t="n">
+        <v>1370</v>
+      </c>
+      <c r="L423" t="n">
+        <v>888</v>
+      </c>
+      <c r="M423" t="n">
+        <v>1685</v>
+      </c>
+      <c r="N423" t="n">
+        <v>930</v>
+      </c>
+      <c r="O423" t="n">
+        <v>876</v>
+      </c>
+      <c r="P423" t="n">
+        <v>1363</v>
+      </c>
+      <c r="Q423" t="n">
+        <v>938</v>
+      </c>
+      <c r="R423" t="n">
+        <v>935</v>
+      </c>
+      <c r="S423" t="n">
+        <v>1280</v>
+      </c>
+      <c r="T423" t="n">
+        <v>1080</v>
+      </c>
+      <c r="U423" t="n">
+        <v>990</v>
+      </c>
+      <c r="V423" t="n">
+        <v>1345</v>
+      </c>
+      <c r="W423" t="n">
+        <v>935</v>
+      </c>
+      <c r="X423" t="n">
+        <v>876</v>
+      </c>
+      <c r="Y423" t="n">
+        <v>1368</v>
+      </c>
+      <c r="Z423" t="n">
+        <v>770</v>
+      </c>
+      <c r="AA423" t="inlineStr"/>
+      <c r="AB423" t="inlineStr"/>
+      <c r="AC423" t="n">
+        <v>871</v>
+      </c>
+      <c r="AD423" t="n">
+        <v>812</v>
+      </c>
+      <c r="AE423" t="n">
+        <v>1450</v>
+      </c>
+      <c r="AF423" t="n">
+        <v>905.9</v>
+      </c>
+      <c r="AG423" t="n">
+        <v>964</v>
+      </c>
+      <c r="AH423" t="inlineStr"/>
+      <c r="AI423" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI423"/>
+  <dimension ref="A1:AI424"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43243,6 +43243,103 @@
       <c r="AH423" t="inlineStr"/>
       <c r="AI423" t="inlineStr"/>
     </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B424" t="n">
+        <v>869.1799999999999</v>
+      </c>
+      <c r="C424" t="n">
+        <v>933</v>
+      </c>
+      <c r="D424" t="inlineStr"/>
+      <c r="E424" t="n">
+        <v>881</v>
+      </c>
+      <c r="F424" t="n">
+        <v>1330</v>
+      </c>
+      <c r="G424" t="n">
+        <v>681.5</v>
+      </c>
+      <c r="H424" t="n">
+        <v>765</v>
+      </c>
+      <c r="I424" t="inlineStr"/>
+      <c r="J424" t="n">
+        <v>675</v>
+      </c>
+      <c r="K424" t="n">
+        <v>1400</v>
+      </c>
+      <c r="L424" t="n">
+        <v>898</v>
+      </c>
+      <c r="M424" t="n">
+        <v>1684</v>
+      </c>
+      <c r="N424" t="n">
+        <v>945</v>
+      </c>
+      <c r="O424" t="n">
+        <v>866</v>
+      </c>
+      <c r="P424" t="n">
+        <v>1418</v>
+      </c>
+      <c r="Q424" t="n">
+        <v>953</v>
+      </c>
+      <c r="R424" t="n">
+        <v>938</v>
+      </c>
+      <c r="S424" t="n">
+        <v>1320</v>
+      </c>
+      <c r="T424" t="n">
+        <v>1098</v>
+      </c>
+      <c r="U424" t="n">
+        <v>978</v>
+      </c>
+      <c r="V424" t="n">
+        <v>1390</v>
+      </c>
+      <c r="W424" t="n">
+        <v>950</v>
+      </c>
+      <c r="X424" t="n">
+        <v>866</v>
+      </c>
+      <c r="Y424" t="n">
+        <v>1423</v>
+      </c>
+      <c r="Z424" t="n">
+        <v>782</v>
+      </c>
+      <c r="AA424" t="inlineStr"/>
+      <c r="AB424" t="inlineStr"/>
+      <c r="AC424" t="n">
+        <v>874</v>
+      </c>
+      <c r="AD424" t="n">
+        <v>789</v>
+      </c>
+      <c r="AE424" t="n">
+        <v>1454</v>
+      </c>
+      <c r="AF424" t="n">
+        <v>921.9299999999999</v>
+      </c>
+      <c r="AG424" t="n">
+        <v>982</v>
+      </c>
+      <c r="AH424" t="inlineStr"/>
+      <c r="AI424" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI424"/>
+  <dimension ref="A1:AI425"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43340,6 +43340,103 @@
       <c r="AH424" t="inlineStr"/>
       <c r="AI424" t="inlineStr"/>
     </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B425" t="n">
+        <v>854.5</v>
+      </c>
+      <c r="C425" t="n">
+        <v>933</v>
+      </c>
+      <c r="D425" t="inlineStr"/>
+      <c r="E425" t="n">
+        <v>860</v>
+      </c>
+      <c r="F425" t="n">
+        <v>1345.75</v>
+      </c>
+      <c r="G425" t="n">
+        <v>681.75</v>
+      </c>
+      <c r="H425" t="n">
+        <v>753</v>
+      </c>
+      <c r="I425" t="inlineStr"/>
+      <c r="J425" t="n">
+        <v>670</v>
+      </c>
+      <c r="K425" t="n">
+        <v>1412</v>
+      </c>
+      <c r="L425" t="n">
+        <v>878</v>
+      </c>
+      <c r="M425" t="n">
+        <v>1695</v>
+      </c>
+      <c r="N425" t="n">
+        <v>925</v>
+      </c>
+      <c r="O425" t="n">
+        <v>843</v>
+      </c>
+      <c r="P425" t="n">
+        <v>1403</v>
+      </c>
+      <c r="Q425" t="n">
+        <v>935</v>
+      </c>
+      <c r="R425" t="n">
+        <v>917</v>
+      </c>
+      <c r="S425" t="n">
+        <v>1331</v>
+      </c>
+      <c r="T425" t="n">
+        <v>1072</v>
+      </c>
+      <c r="U425" t="n">
+        <v>955</v>
+      </c>
+      <c r="V425" t="n">
+        <v>1380</v>
+      </c>
+      <c r="W425" t="n">
+        <v>930</v>
+      </c>
+      <c r="X425" t="n">
+        <v>843</v>
+      </c>
+      <c r="Y425" t="n">
+        <v>1408</v>
+      </c>
+      <c r="Z425" t="n">
+        <v>768</v>
+      </c>
+      <c r="AA425" t="inlineStr"/>
+      <c r="AB425" t="inlineStr"/>
+      <c r="AC425" t="n">
+        <v>884</v>
+      </c>
+      <c r="AD425" t="n">
+        <v>788</v>
+      </c>
+      <c r="AE425" t="n">
+        <v>1439</v>
+      </c>
+      <c r="AF425" t="n">
+        <v>907.96</v>
+      </c>
+      <c r="AG425" t="n">
+        <v>963</v>
+      </c>
+      <c r="AH425" t="inlineStr"/>
+      <c r="AI425" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI425"/>
+  <dimension ref="A1:AI426"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43437,6 +43437,103 @@
       <c r="AH425" t="inlineStr"/>
       <c r="AI425" t="inlineStr"/>
     </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B426" t="n">
+        <v>873.98</v>
+      </c>
+      <c r="C426" t="n">
+        <v>960</v>
+      </c>
+      <c r="D426" t="inlineStr"/>
+      <c r="E426" t="n">
+        <v>885</v>
+      </c>
+      <c r="F426" t="n">
+        <v>1320</v>
+      </c>
+      <c r="G426" t="n">
+        <v>693.25</v>
+      </c>
+      <c r="H426" t="n">
+        <v>768</v>
+      </c>
+      <c r="I426" t="inlineStr"/>
+      <c r="J426" t="n">
+        <v>700</v>
+      </c>
+      <c r="K426" t="n">
+        <v>1406</v>
+      </c>
+      <c r="L426" t="n">
+        <v>898</v>
+      </c>
+      <c r="M426" t="n">
+        <v>1698</v>
+      </c>
+      <c r="N426" t="n">
+        <v>940</v>
+      </c>
+      <c r="O426" t="n">
+        <v>858</v>
+      </c>
+      <c r="P426" t="n">
+        <v>1400</v>
+      </c>
+      <c r="Q426" t="n">
+        <v>960</v>
+      </c>
+      <c r="R426" t="n">
+        <v>937</v>
+      </c>
+      <c r="S426" t="n">
+        <v>1311</v>
+      </c>
+      <c r="T426" t="n">
+        <v>1078</v>
+      </c>
+      <c r="U426" t="n">
+        <v>965</v>
+      </c>
+      <c r="V426" t="n">
+        <v>1350</v>
+      </c>
+      <c r="W426" t="n">
+        <v>945</v>
+      </c>
+      <c r="X426" t="n">
+        <v>858</v>
+      </c>
+      <c r="Y426" t="n">
+        <v>1405</v>
+      </c>
+      <c r="Z426" t="n">
+        <v>770</v>
+      </c>
+      <c r="AA426" t="inlineStr"/>
+      <c r="AB426" t="inlineStr"/>
+      <c r="AC426" t="n">
+        <v>889</v>
+      </c>
+      <c r="AD426" t="n">
+        <v>824</v>
+      </c>
+      <c r="AE426" t="n">
+        <v>1464</v>
+      </c>
+      <c r="AF426" t="n">
+        <v>927.05</v>
+      </c>
+      <c r="AG426" t="n">
+        <v>972</v>
+      </c>
+      <c r="AH426" t="inlineStr"/>
+      <c r="AI426" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
